--- a/data/FIG3.xlsx
+++ b/data/FIG3.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dongjingjing/Desktop/GHG/投稿材料/data and code /data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dongjingjing/Desktop/GHG/FIG/FIG3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A8D0DA-BC4F-D049-9871-0329233EED54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA7CFA8B-22FD-7747-873E-5A087958D42F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4440" yWindow="760" windowWidth="25800" windowHeight="17840" activeTab="3" xr2:uid="{AC41E723-80CD-C04F-8207-2C110BCDC858}"/>
+    <workbookView xWindow="4420" yWindow="660" windowWidth="25820" windowHeight="17840" activeTab="5" xr2:uid="{AC41E723-80CD-C04F-8207-2C110BCDC858}"/>
   </bookViews>
   <sheets>
     <sheet name="Fig.2a" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="128">
   <si>
     <t>Name</t>
   </si>
@@ -68,9 +68,6 @@
   </si>
   <si>
     <t>Anhui</t>
-  </si>
-  <si>
-    <t>BJ</t>
   </si>
   <si>
     <t>Beijing</t>
@@ -437,14 +434,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Emission intensity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>GHG emissions</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>N2O emissions</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
@@ -455,6 +444,57 @@
     <t>CO2 emissions</t>
   </si>
   <si>
+    <t>2023GHG emissions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2010Food crop planting area</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2023Food crop planting area</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>kha</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="等线"/>
+        <family val="4"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <t>2023Food crop yield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2010Food crop yield</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Delta_Yield</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -463,7 +503,34 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Delta_GHG</t>
+    <t>Name2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2010GHG emissions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BJ</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Net GHG emissions</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> Net Emission intensity</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Total</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>BJ</t>
+  </si>
+  <si>
+    <t>Delta_Net_GHG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -475,7 +542,7 @@
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="177" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -531,6 +598,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Helvetica Neue"/>
@@ -556,6 +630,19 @@
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF333333"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -579,7 +666,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -619,32 +706,77 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="177" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="176" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -983,16 +1115,20 @@
   <dimension ref="A1:O33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="10.83203125" style="1"/>
+    <col min="1" max="1" width="10.83203125" style="1"/>
+    <col min="2" max="2" width="15" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" style="1"/>
+    <col min="5" max="5" width="17" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.83203125" style="3"/>
-    <col min="7" max="8" width="10.83203125" style="1"/>
+    <col min="7" max="7" width="10.83203125" style="1"/>
+    <col min="8" max="8" width="17" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="10.83203125" style="1"/>
+    <col min="12" max="12" width="12.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="10.83203125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -1000,16 +1136,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>109</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>1</v>
@@ -1021,62 +1157,67 @@
         <v>3</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:15">
-      <c r="A3" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="1">
-        <v>63.754251388123301</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="A3" s="34" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="33">
+        <v>58.942717461710295</v>
+      </c>
+      <c r="C3" s="10">
         <v>7334.46</v>
       </c>
       <c r="D3" s="1">
         <v>61.955119427962899</v>
       </c>
       <c r="E3" s="1">
-        <v>0.64970725168498999</v>
+        <f>B3*100000/1000/C3</f>
+        <v>0.80364086056383555</v>
+      </c>
+      <c r="F3" s="3">
+        <f>B3*1000000/C3/1000</f>
+        <v>8.0364086056383552</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>8</v>
@@ -1102,30 +1243,35 @@
       </c>
       <c r="N3" s="1">
         <f>B3*1000/I3</f>
-        <v>8.6924260801917654</v>
+        <v>8.0364086056383552</v>
       </c>
       <c r="O3" s="1">
         <v>63.754251388123301</v>
       </c>
     </row>
     <row r="4" spans="1:15">
-      <c r="A4" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="1">
-        <v>0.63927810489742598</v>
-      </c>
-      <c r="C4" s="1">
+      <c r="A4" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="33">
+        <v>0.72296990075272094</v>
+      </c>
+      <c r="C4" s="10">
         <v>89.47</v>
       </c>
       <c r="D4" s="2">
         <v>99.594893199116129</v>
       </c>
       <c r="E4" s="1">
-        <v>0.811379549586008</v>
+        <f t="shared" ref="E4:E33" si="0">B4*100000/1000/C4</f>
+        <v>0.80805845618947247</v>
+      </c>
+      <c r="F4" s="3">
+        <f t="shared" ref="F4:F33" si="1">B4*1000000/C4/1000</f>
+        <v>8.0805845618947227</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H4" s="1">
         <v>158.97999999999999</v>
@@ -1143,7 +1289,7 @@
         <v>81.13</v>
       </c>
       <c r="M4" s="1">
-        <f t="shared" ref="M4:M33" si="0">L4/(K4+L4)*100</f>
+        <f t="shared" ref="M4:M33" si="2">L4/(K4+L4)*100</f>
         <v>99.594893199116129</v>
       </c>
       <c r="O4" s="1">
@@ -1151,23 +1297,28 @@
       </c>
     </row>
     <row r="5" spans="1:15">
-      <c r="A5" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="1">
-        <v>11.205703806285699</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="A5" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="33">
+        <v>10.723820296945991</v>
+      </c>
+      <c r="C5" s="10">
         <v>2025.93</v>
       </c>
       <c r="D5" s="1">
         <v>41.559481240326626</v>
       </c>
       <c r="E5" s="1">
-        <v>0.48304850127955828</v>
+        <f t="shared" si="0"/>
+        <v>0.52932827377777081</v>
+      </c>
+      <c r="F5" s="3">
+        <f t="shared" si="1"/>
+        <v>5.2932827377777079</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H5" s="1">
         <v>3506.19</v>
@@ -1185,7 +1336,7 @@
         <v>467.22</v>
       </c>
       <c r="M5" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>41.559481240326626</v>
       </c>
       <c r="O5" s="1">
@@ -1193,23 +1344,28 @@
       </c>
     </row>
     <row r="6" spans="1:15">
-      <c r="A6" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="1">
-        <v>8.4311774242604098</v>
-      </c>
-      <c r="C6" s="1">
+      <c r="A6" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="33">
+        <v>7.6487337451780926</v>
+      </c>
+      <c r="C6" s="10">
         <v>841.1</v>
       </c>
       <c r="D6" s="1">
         <v>5.6727238489784382</v>
       </c>
       <c r="E6" s="1">
-        <v>0.81316002479426397</v>
+        <f t="shared" si="0"/>
+        <v>0.90937269589562386</v>
+      </c>
+      <c r="F6" s="3">
+        <f t="shared" si="1"/>
+        <v>9.0937269589562391</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H6" s="1">
         <v>1712.25</v>
@@ -1227,7 +1383,7 @@
         <v>36.15</v>
       </c>
       <c r="M6" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5.6727238489784382</v>
       </c>
       <c r="O6" s="1">
@@ -1235,23 +1391,28 @@
       </c>
     </row>
     <row r="7" spans="1:15">
-      <c r="A7" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="1">
-        <v>9.1647128290918296</v>
-      </c>
-      <c r="C7" s="1">
+      <c r="A7" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="33">
+        <v>25.221590456396985</v>
+      </c>
+      <c r="C7" s="10">
         <v>2710.93</v>
       </c>
       <c r="D7" s="1">
         <v>99.87565228251367</v>
       </c>
       <c r="E7" s="1">
-        <v>0.35389836947489017</v>
+        <f t="shared" si="0"/>
+        <v>0.9303667175617587</v>
+      </c>
+      <c r="F7" s="3">
+        <f t="shared" si="1"/>
+        <v>9.303667175617587</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H7" s="1">
         <v>4139.59</v>
@@ -1269,7 +1430,7 @@
         <v>1839.32</v>
       </c>
       <c r="M7" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>99.87565228251367</v>
       </c>
       <c r="O7" s="1">
@@ -1277,23 +1438,28 @@
       </c>
     </row>
     <row r="8" spans="1:15">
-      <c r="A8" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="1">
-        <v>28.5327119569614</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="A8" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="33">
+        <v>10.127456556009038</v>
+      </c>
+      <c r="C8" s="10">
         <v>2229.5100000000002</v>
       </c>
       <c r="D8" s="1">
         <v>6.8638842174998729</v>
       </c>
       <c r="E8" s="1">
-        <v>0.77020752762723133</v>
+        <f t="shared" si="0"/>
+        <v>0.45424584576920651</v>
+      </c>
+      <c r="F8" s="3">
+        <f t="shared" si="1"/>
+        <v>4.5424584576920664</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H8" s="1">
         <v>4587.2700000000004</v>
@@ -1311,7 +1477,7 @@
         <v>134.69</v>
       </c>
       <c r="M8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>6.8638842174998729</v>
       </c>
       <c r="O8" s="1">
@@ -1319,23 +1485,28 @@
       </c>
     </row>
     <row r="9" spans="1:15">
-      <c r="A9" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="1">
-        <v>27.955852360962599</v>
-      </c>
-      <c r="C9" s="1">
+      <c r="A9" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="33">
+        <v>25.123575264253095</v>
+      </c>
+      <c r="C9" s="10">
         <v>2834.72</v>
       </c>
       <c r="D9" s="1">
         <v>26.076880447377697</v>
       </c>
       <c r="E9" s="1">
-        <v>0.66260831017876165</v>
+        <f t="shared" si="0"/>
+        <v>0.88628066490704893</v>
+      </c>
+      <c r="F9" s="3">
+        <f t="shared" si="1"/>
+        <v>8.8628066490704889</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H9" s="1">
         <v>6352.35</v>
@@ -1353,7 +1524,7 @@
         <v>621.12</v>
       </c>
       <c r="M9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>26.076880447377697</v>
       </c>
       <c r="O9" s="1">
@@ -1361,23 +1532,28 @@
       </c>
     </row>
     <row r="10" spans="1:15">
-      <c r="A10" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="1">
-        <v>10.8436199827926</v>
-      </c>
-      <c r="C10" s="1">
+      <c r="A10" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="33">
+        <v>10.211564386096354</v>
+      </c>
+      <c r="C10" s="10">
         <v>2773.8</v>
       </c>
       <c r="D10" s="1">
         <v>58.164277276240753</v>
       </c>
       <c r="E10" s="1">
-        <v>0.33659971365982705</v>
+        <f t="shared" si="0"/>
+        <v>0.36814349939059604</v>
+      </c>
+      <c r="F10" s="3">
+        <f t="shared" si="1"/>
+        <v>3.6814349939059605</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H10" s="1">
         <v>5344.29</v>
@@ -1395,7 +1571,7 @@
         <v>797.63</v>
       </c>
       <c r="M10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>58.164277276240753</v>
       </c>
       <c r="O10" s="1">
@@ -1403,23 +1579,28 @@
       </c>
     </row>
     <row r="11" spans="1:15">
-      <c r="A11" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="1">
-        <v>3.9925030934546397</v>
-      </c>
-      <c r="C11" s="1">
+      <c r="A11" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="33">
+        <v>3.6373529412489014</v>
+      </c>
+      <c r="C11" s="10">
         <v>273.58999999999997</v>
       </c>
       <c r="D11" s="1">
         <v>0</v>
       </c>
       <c r="E11" s="1">
-        <v>1.1480648397668343</v>
+        <f t="shared" si="0"/>
+        <v>1.3294904569790202</v>
+      </c>
+      <c r="F11" s="3">
+        <f t="shared" si="1"/>
+        <v>13.294904569790202</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H11" s="1">
         <v>702.36</v>
@@ -1437,7 +1618,7 @@
         <v>0</v>
       </c>
       <c r="M11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O11" s="1">
@@ -1445,23 +1626,28 @@
       </c>
     </row>
     <row r="12" spans="1:15">
-      <c r="A12" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" s="1">
-        <v>35.591325709347004</v>
-      </c>
-      <c r="C12" s="1">
+      <c r="A12" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="33">
+        <v>39.568015713843018</v>
+      </c>
+      <c r="C12" s="10">
         <v>6455.19</v>
       </c>
       <c r="D12" s="1">
         <v>98.724884616719294</v>
       </c>
       <c r="E12" s="1">
-        <v>0.59865937537952085</v>
+        <f t="shared" si="0"/>
+        <v>0.61296438546104792</v>
+      </c>
+      <c r="F12" s="3">
+        <f t="shared" si="1"/>
+        <v>6.129643854610479</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H12" s="1">
         <v>8098.23</v>
@@ -1479,7 +1665,7 @@
         <v>5689.91</v>
       </c>
       <c r="M12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>98.724884616719294</v>
       </c>
       <c r="O12" s="1">
@@ -1487,23 +1673,28 @@
       </c>
     </row>
     <row r="13" spans="1:15">
-      <c r="A13" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="1">
-        <v>102.910368100078</v>
-      </c>
-      <c r="C13" s="1">
+      <c r="A13" s="34" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="33">
+        <v>70.717559493479058</v>
+      </c>
+      <c r="C13" s="10">
         <v>14743.09</v>
       </c>
       <c r="D13" s="2">
         <v>66.440509510716112</v>
       </c>
       <c r="E13" s="1">
-        <v>0.41816642298579593</v>
+        <f t="shared" si="0"/>
+        <v>0.47966579254063468</v>
+      </c>
+      <c r="F13" s="3">
+        <f t="shared" si="1"/>
+        <v>4.7966579254063468</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H13" s="1">
         <v>15304.22</v>
@@ -1521,7 +1712,7 @@
         <v>6471</v>
       </c>
       <c r="M13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>66.440509510716112</v>
       </c>
       <c r="O13" s="1">
@@ -1529,23 +1720,28 @@
       </c>
     </row>
     <row r="14" spans="1:15">
-      <c r="A14" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="1">
-        <v>64.932612477067593</v>
-      </c>
-      <c r="C14" s="1">
+      <c r="A14" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="33">
+        <v>94.394767008528305</v>
+      </c>
+      <c r="C14" s="10">
         <v>10785.29</v>
       </c>
       <c r="D14" s="1">
         <v>94.174746750627875</v>
       </c>
       <c r="E14" s="1">
-        <v>0.59469591155291823</v>
+        <f t="shared" si="0"/>
+        <v>0.87521769937135019</v>
+      </c>
+      <c r="F14" s="3">
+        <f t="shared" si="1"/>
+        <v>8.752176993713503</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H14" s="1">
         <v>14747.14</v>
@@ -1563,7 +1759,7 @@
         <v>9550.44</v>
       </c>
       <c r="M14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>94.174746750627875</v>
       </c>
       <c r="O14" s="1">
@@ -1571,23 +1767,28 @@
       </c>
     </row>
     <row r="15" spans="1:15">
-      <c r="A15" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" s="1">
-        <v>51.2057013284115</v>
-      </c>
-      <c r="C15" s="1">
+      <c r="A15" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="33">
+        <v>46.163253907706853</v>
+      </c>
+      <c r="C15" s="10">
         <v>4706.97</v>
       </c>
       <c r="D15" s="1">
         <v>44.231396446656937</v>
       </c>
       <c r="E15" s="1">
-        <v>0.79678333004515867</v>
+        <f t="shared" si="0"/>
+        <v>0.9807424714350601</v>
+      </c>
+      <c r="F15" s="3">
+        <f t="shared" si="1"/>
+        <v>9.8074247143505993</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H15" s="1">
         <v>8309.25</v>
@@ -1605,7 +1806,7 @@
         <v>1803.69</v>
       </c>
       <c r="M15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>44.231396446656937</v>
       </c>
       <c r="O15" s="1">
@@ -1613,23 +1814,28 @@
       </c>
     </row>
     <row r="16" spans="1:15">
-      <c r="A16" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="1">
-        <v>51.3802766474682</v>
-      </c>
-      <c r="C16" s="1">
+      <c r="A16" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="33">
+        <v>44.958510439192324</v>
+      </c>
+      <c r="C16" s="10">
         <v>4763.4799999999996</v>
       </c>
       <c r="D16" s="1">
         <v>9.8175096591700992</v>
       </c>
       <c r="E16" s="1">
-        <v>0.66599717908953404</v>
+        <f t="shared" si="0"/>
+        <v>0.94381650472327638</v>
+      </c>
+      <c r="F16" s="3">
+        <f t="shared" si="1"/>
+        <v>9.4381650472327632</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H16" s="1">
         <v>8714.9500000000007</v>
@@ -1647,7 +1853,7 @@
         <v>429.68</v>
       </c>
       <c r="M16" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9.8175096591700992</v>
       </c>
       <c r="O16" s="1">
@@ -1655,23 +1861,28 @@
       </c>
     </row>
     <row r="17" spans="1:15">
-      <c r="A17" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B17" s="1">
-        <v>23.076820585871999</v>
-      </c>
-      <c r="C17" s="1">
+      <c r="A17" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="33">
+        <v>34.218511569548681</v>
+      </c>
+      <c r="C17" s="10">
         <v>6984.73</v>
       </c>
       <c r="D17" s="1">
         <v>97.838490831037788</v>
       </c>
       <c r="E17" s="1">
-        <v>0.30874401153065301</v>
+        <f t="shared" si="0"/>
+        <v>0.48990457139429416</v>
+      </c>
+      <c r="F17" s="3">
+        <f t="shared" si="1"/>
+        <v>4.8990457139429422</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="H17" s="1">
         <v>8808.8700000000008</v>
@@ -1689,7 +1900,7 @@
         <v>4681.2</v>
       </c>
       <c r="M17" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>97.838490831037788</v>
       </c>
       <c r="O17" s="1">
@@ -1697,23 +1908,28 @@
       </c>
     </row>
     <row r="18" spans="1:15">
-      <c r="A18" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" s="1">
-        <v>54.226255533743597</v>
-      </c>
-      <c r="C18" s="1">
+      <c r="A18" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="33">
+        <v>50.054313882637047</v>
+      </c>
+      <c r="C18" s="10">
         <v>5458.94</v>
       </c>
       <c r="D18" s="1">
         <v>56.440766055090855</v>
       </c>
       <c r="E18" s="1">
-        <v>0.66420377440342948</v>
+        <f t="shared" si="0"/>
+        <v>0.91692368633172461</v>
+      </c>
+      <c r="F18" s="3">
+        <f t="shared" si="1"/>
+        <v>9.1692368633172467</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H18" s="1">
         <v>7589.96</v>
@@ -1731,7 +1947,7 @@
         <v>2877.83</v>
       </c>
       <c r="M18" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>56.440766055090855</v>
       </c>
       <c r="O18" s="1">
@@ -1739,23 +1955,28 @@
       </c>
     </row>
     <row r="19" spans="1:15">
-      <c r="A19" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="1">
-        <v>44.630474100349097</v>
-      </c>
-      <c r="C19" s="1">
+      <c r="A19" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="33">
+        <v>37.911175699307741</v>
+      </c>
+      <c r="C19" s="10">
         <v>3774.29</v>
       </c>
       <c r="D19" s="1">
         <v>2.0791554895781785</v>
       </c>
       <c r="E19" s="1">
-        <v>0.64495603972970061</v>
+        <f t="shared" si="0"/>
+        <v>1.0044584729659816</v>
+      </c>
+      <c r="F19" s="3">
+        <f t="shared" si="1"/>
+        <v>10.044584729659816</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="H19" s="1">
         <v>5797.01</v>
@@ -1773,7 +1994,7 @@
         <v>71.849999999999994</v>
       </c>
       <c r="M19" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2.0791554895781785</v>
       </c>
       <c r="O19" s="1">
@@ -1781,23 +2002,28 @@
       </c>
     </row>
     <row r="20" spans="1:15">
-      <c r="A20" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" s="1">
-        <v>35.1514318805446</v>
-      </c>
-      <c r="C20" s="1">
+      <c r="A20" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="33">
+        <v>20.796616893488086</v>
+      </c>
+      <c r="C20" s="10">
         <v>5825.61</v>
       </c>
       <c r="D20" s="1">
         <v>84.589009893810285</v>
       </c>
       <c r="E20" s="1">
-        <v>0.49131590296117317</v>
+        <f t="shared" si="0"/>
+        <v>0.35698608203240667</v>
+      </c>
+      <c r="F20" s="3">
+        <f t="shared" si="1"/>
+        <v>3.5698608203240672</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H20" s="1">
         <v>6292.47</v>
@@ -1815,7 +2041,7 @@
         <v>4549.29</v>
       </c>
       <c r="M20" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>84.589009893810285</v>
       </c>
       <c r="O20" s="1">
@@ -1823,23 +2049,28 @@
       </c>
     </row>
     <row r="21" spans="1:15">
-      <c r="A21" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B21" s="1">
-        <v>20.330273313474901</v>
-      </c>
-      <c r="C21" s="1">
+      <c r="A21" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="33">
+        <v>23.558404117466363</v>
+      </c>
+      <c r="C21" s="10">
         <v>3578.39</v>
       </c>
       <c r="D21" s="1">
         <v>84.863671420146076</v>
       </c>
       <c r="E21" s="1">
-        <v>0.49657087099618941</v>
+        <f t="shared" si="0"/>
+        <v>0.65835205546255071</v>
+      </c>
+      <c r="F21" s="3">
+        <f t="shared" si="1"/>
+        <v>6.5835205546255064</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H21" s="1">
         <v>4361.42</v>
@@ -1857,7 +2088,7 @@
         <v>2805.89</v>
       </c>
       <c r="M21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>84.863671420146076</v>
       </c>
       <c r="O21" s="1">
@@ -1865,23 +2096,28 @@
       </c>
     </row>
     <row r="22" spans="1:15">
-      <c r="A22" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" s="1">
-        <v>3.7188301006580202</v>
-      </c>
-      <c r="C22" s="1">
+      <c r="A22" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="33">
+        <v>3.7048392097787901</v>
+      </c>
+      <c r="C22" s="10">
         <v>693.89</v>
       </c>
       <c r="D22" s="1">
         <v>95.801510788364425</v>
       </c>
       <c r="E22" s="1">
-        <v>0.44456924396884612</v>
+        <f t="shared" si="0"/>
+        <v>0.53392313043548556</v>
+      </c>
+      <c r="F22" s="3">
+        <f t="shared" si="1"/>
+        <v>5.3392313043548549</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H22" s="1">
         <v>1199.0999999999999</v>
@@ -1899,7 +2135,7 @@
         <v>459.1</v>
       </c>
       <c r="M22" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>95.801510788364425</v>
       </c>
       <c r="O22" s="1">
@@ -1907,23 +2143,28 @@
       </c>
     </row>
     <row r="23" spans="1:15">
-      <c r="A23" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1.49839358609969</v>
-      </c>
-      <c r="C23" s="1">
+      <c r="A23" s="34" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="33">
+        <v>1.5875475900252078</v>
+      </c>
+      <c r="C23" s="10">
         <v>304.89999999999998</v>
       </c>
       <c r="D23" s="1">
         <v>100</v>
       </c>
       <c r="E23" s="1">
-        <v>0.54429418788991912</v>
+        <f t="shared" si="0"/>
+        <v>0.52067812070357755</v>
+      </c>
+      <c r="F23" s="3">
+        <f t="shared" si="1"/>
+        <v>5.2067812070357755</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H23" s="1">
         <v>598.79999999999995</v>
@@ -1941,7 +2182,7 @@
         <v>123.81</v>
       </c>
       <c r="M23" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="O23" s="1">
@@ -1949,23 +2190,28 @@
       </c>
     </row>
     <row r="24" spans="1:15">
-      <c r="A24" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="1">
-        <v>11.785400439105899</v>
-      </c>
-      <c r="C24" s="1">
+      <c r="A24" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="33">
+        <v>33.370951281191928</v>
+      </c>
+      <c r="C24" s="10">
         <v>3022.97</v>
       </c>
       <c r="D24" s="1">
         <v>95.332076039702144</v>
       </c>
       <c r="E24" s="1">
-        <v>0.3905461287046989</v>
+        <f t="shared" si="0"/>
+        <v>1.1039127507448612</v>
+      </c>
+      <c r="F24" s="3">
+        <f t="shared" si="1"/>
+        <v>11.039127507448612</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H24" s="1">
         <v>4239.9399999999996</v>
@@ -1983,7 +2229,7 @@
         <v>2153.38</v>
       </c>
       <c r="M24" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>95.332076039702144</v>
       </c>
       <c r="O24" s="1">
@@ -1991,23 +2237,28 @@
       </c>
     </row>
     <row r="25" spans="1:15">
-      <c r="A25" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" s="1">
-        <v>44.248998114810604</v>
-      </c>
-      <c r="C25" s="1">
+      <c r="A25" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="33">
+        <v>49.924356130133489</v>
+      </c>
+      <c r="C25" s="10">
         <v>8387.9</v>
       </c>
       <c r="D25" s="2">
         <v>98.735941874099751</v>
       </c>
       <c r="E25" s="1">
-        <v>0.55225730545554685</v>
+        <f t="shared" si="0"/>
+        <v>0.59519493711338334</v>
+      </c>
+      <c r="F25" s="3">
+        <f t="shared" si="1"/>
+        <v>5.9519493711338347</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H25" s="1">
         <v>11002.72</v>
@@ -2025,7 +2276,7 @@
         <v>7889.92</v>
       </c>
       <c r="M25" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>98.735941874099751</v>
       </c>
       <c r="O25" s="1">
@@ -2033,23 +2284,28 @@
       </c>
     </row>
     <row r="26" spans="1:15">
-      <c r="A26" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B26" s="1">
-        <v>1.6502778051918301</v>
-      </c>
-      <c r="C26" s="1">
+      <c r="A26" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="33">
+        <v>1.6271182138652531</v>
+      </c>
+      <c r="C26" s="10">
         <v>127.17</v>
       </c>
       <c r="D26" s="1">
         <v>15.683581124757598</v>
       </c>
       <c r="E26" s="1">
-        <v>1.0126599178767217</v>
+        <f t="shared" si="0"/>
+        <v>1.2794827505427799</v>
+      </c>
+      <c r="F26" s="3">
+        <f t="shared" si="1"/>
+        <v>12.794827505427799</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H26" s="1">
         <v>273.2</v>
@@ -2067,7 +2323,7 @@
         <v>19.41</v>
       </c>
       <c r="M26" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>15.683581124757598</v>
       </c>
       <c r="O26" s="1">
@@ -2075,23 +2331,28 @@
       </c>
     </row>
     <row r="27" spans="1:15">
-      <c r="A27" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="B27" s="1">
-        <v>7.35322901837527</v>
-      </c>
-      <c r="C27" s="1">
+      <c r="A27" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="33">
+        <v>12.367138769613588</v>
+      </c>
+      <c r="C27" s="10">
         <v>3160.96</v>
       </c>
       <c r="D27" s="1">
         <v>99.90715417029017</v>
       </c>
       <c r="E27" s="1">
-        <v>0.25357309522797877</v>
+        <f t="shared" si="0"/>
+        <v>0.39124629130433758</v>
+      </c>
+      <c r="F27" s="3">
+        <f t="shared" si="1"/>
+        <v>3.9124629130433757</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H27" s="1">
         <v>3641.72</v>
@@ -2109,7 +2370,7 @@
         <v>2378.08</v>
       </c>
       <c r="M27" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>99.90715417029017</v>
       </c>
       <c r="O27" s="1">
@@ -2117,23 +2378,28 @@
       </c>
     </row>
     <row r="28" spans="1:15">
-      <c r="A28" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" s="1">
-        <v>34.9867729267092</v>
-      </c>
-      <c r="C28" s="1">
+      <c r="A28" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="33">
+        <v>8.5284683512363202</v>
+      </c>
+      <c r="C28" s="10">
         <v>6403.97</v>
       </c>
       <c r="D28" s="1">
         <v>57.130244877096793</v>
       </c>
       <c r="E28" s="1">
-        <v>0.4229212458899782</v>
+        <f t="shared" si="0"/>
+        <v>0.13317470805197901</v>
+      </c>
+      <c r="F28" s="3">
+        <f t="shared" si="1"/>
+        <v>1.3317470805197902</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H28" s="1">
         <v>10264.41</v>
@@ -2151,7 +2417,7 @@
         <v>2459</v>
       </c>
       <c r="M28" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>57.130244877096793</v>
       </c>
       <c r="O28" s="1">
@@ -2159,23 +2425,28 @@
       </c>
     </row>
     <row r="29" spans="1:15">
-      <c r="A29" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" s="1">
-        <v>1.0236397426138699</v>
-      </c>
-      <c r="C29" s="1">
+      <c r="A29" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="33">
+        <v>1.3807077502937468</v>
+      </c>
+      <c r="C29" s="10">
         <v>390.03</v>
       </c>
       <c r="D29" s="1">
         <v>85.469394355947287</v>
       </c>
       <c r="E29" s="1">
-        <v>0.412109477847306</v>
+        <f t="shared" si="0"/>
+        <v>0.35400039748064172</v>
+      </c>
+      <c r="F29" s="3">
+        <f t="shared" si="1"/>
+        <v>3.5400039748064174</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H29" s="1">
         <v>453.1</v>
@@ -2193,7 +2464,7 @@
         <v>317.10000000000002</v>
       </c>
       <c r="M29" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>85.469394355947287</v>
       </c>
       <c r="O29" s="1">
@@ -2201,23 +2472,28 @@
       </c>
     </row>
     <row r="30" spans="1:15">
-      <c r="A30" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="1">
-        <v>2.7539266603843</v>
-      </c>
-      <c r="C30" s="1">
-        <v>194.58</v>
+      <c r="A30" s="34" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="33">
+        <v>16.357622467507575</v>
+      </c>
+      <c r="C30" s="10">
+        <v>2824.76</v>
       </c>
       <c r="D30" s="1">
         <v>97.779499096307774</v>
       </c>
       <c r="E30" s="1">
-        <v>1.1349028328802211</v>
+        <f t="shared" si="0"/>
+        <v>0.57908007998936462</v>
+      </c>
+      <c r="F30" s="3">
+        <f t="shared" si="1"/>
+        <v>5.7908007998936455</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H30" s="1">
         <v>281.39999999999998</v>
@@ -2235,7 +2511,7 @@
         <v>37.869999999999997</v>
       </c>
       <c r="M30" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>97.779499096307774</v>
       </c>
       <c r="O30" s="1">
@@ -2243,23 +2519,28 @@
       </c>
     </row>
     <row r="31" spans="1:15">
-      <c r="A31" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="B31" s="1">
-        <v>15.8765366820744</v>
-      </c>
-      <c r="C31" s="1">
-        <v>2824.76</v>
+      <c r="A31" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="33">
+        <v>2.8040034286631066</v>
+      </c>
+      <c r="C31" s="12">
+        <v>194.58</v>
       </c>
       <c r="D31" s="2">
         <v>98.524118472527761</v>
       </c>
       <c r="E31" s="1">
-        <v>0.57504479680921472</v>
+        <f t="shared" si="0"/>
+        <v>1.4410542854677286</v>
+      </c>
+      <c r="F31" s="3">
+        <f t="shared" si="1"/>
+        <v>14.410542854677287</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H31" s="1">
         <v>6839.83</v>
@@ -2277,7 +2558,7 @@
         <v>2646.88</v>
       </c>
       <c r="M31" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>98.524118472527761</v>
       </c>
       <c r="O31" s="1">
@@ -2285,23 +2566,28 @@
       </c>
     </row>
     <row r="32" spans="1:15">
-      <c r="A32" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="1">
-        <v>15.0672144135737</v>
-      </c>
-      <c r="C32" s="1">
+      <c r="A32" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="33">
+        <v>14.666241271003578</v>
+      </c>
+      <c r="C32" s="10">
         <v>4243.22</v>
       </c>
       <c r="D32" s="1">
         <v>76.298746324957008</v>
       </c>
       <c r="E32" s="1">
-        <v>0.31720610720667036</v>
+        <f t="shared" si="0"/>
+        <v>0.34563942644980877</v>
+      </c>
+      <c r="F32" s="3">
+        <f t="shared" si="1"/>
+        <v>3.4563942644980878</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H32" s="1">
         <v>7218.08</v>
@@ -2319,7 +2605,7 @@
         <v>2200.6999999999998</v>
       </c>
       <c r="M32" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>76.298746324957008</v>
       </c>
       <c r="O32" s="1">
@@ -2327,23 +2613,28 @@
       </c>
     </row>
     <row r="33" spans="1:15">
-      <c r="A33" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="1">
-        <v>10.131742999654001</v>
-      </c>
-      <c r="C33" s="1">
+      <c r="A33" s="34" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="33">
+        <v>9.212759004577574</v>
+      </c>
+      <c r="C33" s="10">
         <v>1024.68</v>
       </c>
       <c r="D33" s="1">
         <v>21.770995310936726</v>
       </c>
       <c r="E33" s="1">
-        <v>0.75050263355435243</v>
+        <f t="shared" si="0"/>
+        <v>0.89908644694710282</v>
+      </c>
+      <c r="F33" s="3">
+        <f t="shared" si="1"/>
+        <v>8.9908644694710276</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H33" s="1">
         <v>2041.38</v>
@@ -2361,7 +2652,7 @@
         <v>180.61</v>
       </c>
       <c r="M33" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>21.770995310936726</v>
       </c>
       <c r="O33" s="1">
@@ -2377,7 +2668,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC02337-34E5-C844-8D74-9D50CE44E96C}">
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:AG85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="10"/>
@@ -2385,51 +2676,51 @@
     <col min="3" max="3" width="21.6640625" style="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" style="10"/>
     <col min="5" max="5" width="24.83203125" style="10" customWidth="1"/>
-    <col min="6" max="11" width="10.83203125" style="14"/>
-    <col min="12" max="12" width="19.6640625" style="14" customWidth="1"/>
-    <col min="13" max="16384" width="10.83203125" style="14"/>
+    <col min="6" max="11" width="10.83203125" style="21"/>
+    <col min="12" max="12" width="19.6640625" style="21" customWidth="1"/>
+    <col min="13" max="16384" width="10.83203125" style="21"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C1" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>108</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>109</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="10" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B2" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>101</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="14">
-        <v>8.7754675202325796</v>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3">
+        <v>9.0241048463151702E-2</v>
       </c>
       <c r="C3" s="10">
         <v>7334.46</v>
@@ -2438,36 +2729,42 @@
         <v>61.955119427962899</v>
       </c>
       <c r="E3" s="9">
-        <v>4.9712140388017599E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="14">
-        <v>0.29252235051385317</v>
+        <v>1.2303707220865844E-2</v>
+      </c>
+      <c r="H3" s="35"/>
+      <c r="L3" s="32"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="B4" s="3">
+        <v>2.5850018706651857E-3</v>
       </c>
       <c r="C4" s="10">
         <v>89.47</v>
       </c>
-      <c r="D4" s="21">
+      <c r="D4" s="30">
         <v>99.594893199116129</v>
       </c>
       <c r="E4" s="9">
-        <v>0.11320072519367995</v>
-      </c>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="N4" s="19"/>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" s="14">
-        <v>2.8223667204715022</v>
+        <v>2.8892387064548854E-2</v>
+      </c>
+      <c r="H4" s="35"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1.6267974419838165E-2</v>
       </c>
       <c r="C5" s="10">
         <v>2025.93</v>
@@ -2476,15 +2773,20 @@
         <v>41.559481240326626</v>
       </c>
       <c r="E5" s="9">
-        <v>6.6795211552632738E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" s="14">
-        <v>2.3796328244049629</v>
+        <v>8.0298798180777047E-3</v>
+      </c>
+      <c r="H5" s="35"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="37" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1.2916529734166448E-2</v>
       </c>
       <c r="C6" s="10">
         <v>841.1</v>
@@ -2493,15 +2795,20 @@
         <v>5.6727238489784382</v>
       </c>
       <c r="E6" s="9">
-        <v>0.10757041243188108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B7" s="14">
-        <v>2.8075162199240138</v>
+        <v>1.5356711133237959E-2</v>
+      </c>
+      <c r="H6" s="35"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="3">
+        <v>3.1472291464855535E-2</v>
       </c>
       <c r="C7" s="10">
         <v>2710.93</v>
@@ -2510,15 +2817,20 @@
         <v>99.87565228251367</v>
       </c>
       <c r="E7" s="9">
-        <v>3.4754226610080735E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B8" s="14">
-        <v>5.1061753482587537</v>
+        <v>1.160940764418688E-2</v>
+      </c>
+      <c r="H7" s="35"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3">
+        <v>3.5752437585692187E-2</v>
       </c>
       <c r="C8" s="10">
         <v>2229.5100000000002</v>
@@ -2527,15 +2839,20 @@
         <v>6.8638842174998729</v>
       </c>
       <c r="E8" s="9">
-        <v>9.0957416898465204E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="14">
-        <v>4.9321225003280578</v>
+        <v>1.6036006829165238E-2</v>
+      </c>
+      <c r="H8" s="35"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="37" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="3">
+        <v>3.7214936972646336E-2</v>
       </c>
       <c r="C9" s="10">
         <v>2834.72</v>
@@ -2544,15 +2861,20 @@
         <v>26.076880447377697</v>
       </c>
       <c r="E9" s="9">
-        <v>7.0415053163522784E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="B10" s="14">
-        <v>2.4361586974532159</v>
+        <v>1.312825851323811E-2</v>
+      </c>
+      <c r="H9" s="35"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1.8340333727534224E-2</v>
       </c>
       <c r="C10" s="10">
         <v>2773.8</v>
@@ -2561,15 +2883,20 @@
         <v>58.164277276240753</v>
       </c>
       <c r="E10" s="9">
-        <v>3.9188721262240829E-2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" s="14">
-        <v>0.96327186938434695</v>
+        <v>6.611988509457864E-3</v>
+      </c>
+      <c r="H10" s="35"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="3">
+        <v>5.9244363257736042E-3</v>
       </c>
       <c r="C11" s="10">
         <v>273.58999999999997</v>
@@ -2578,15 +2905,20 @@
         <v>0</v>
       </c>
       <c r="E11" s="9">
-        <v>0.19412469190549339</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" s="14">
-        <v>10.534800332930701</v>
+        <v>2.1654433004764811E-2</v>
+      </c>
+      <c r="H11" s="35"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.13775242613471234</v>
       </c>
       <c r="C12" s="10">
         <v>6455.19</v>
@@ -2595,34 +2927,42 @@
         <v>98.724884616719294</v>
       </c>
       <c r="E12" s="9">
-        <v>5.4134292037378191E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="14">
-        <v>13.408607302815932</v>
+        <v>2.1339794201985122E-2</v>
+      </c>
+      <c r="H12" s="35"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.22053012491909113</v>
       </c>
       <c r="C13" s="10">
         <v>14743.09</v>
       </c>
-      <c r="D13" s="21">
+      <c r="D13" s="30">
         <v>66.440509510716112</v>
       </c>
       <c r="E13" s="9">
-        <v>3.3722945434491121E-2</v>
-      </c>
-      <c r="I13" s="19"/>
-      <c r="N13" s="19"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="14">
-        <v>21.459619831233443</v>
+        <v>1.4958202447322178E-2</v>
+      </c>
+      <c r="H13" s="35"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="3">
+        <v>0.11261321571888083</v>
       </c>
       <c r="C14" s="10">
         <v>10785.29</v>
@@ -2631,17 +2971,20 @@
         <v>94.174746750627875</v>
       </c>
       <c r="E14" s="9">
-        <v>6.7021847849180652E-2</v>
-      </c>
-      <c r="H14" s="19"/>
-      <c r="J14" s="19"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="B15" s="14">
-        <v>7.3734062318024183</v>
+        <v>1.044137113780722E-2</v>
+      </c>
+      <c r="H14" s="35"/>
+      <c r="L14" s="32"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" s="3">
+        <v>6.4922905700836697E-2</v>
       </c>
       <c r="C15" s="10">
         <v>4706.97</v>
@@ -2650,15 +2993,20 @@
         <v>44.231396446656937</v>
       </c>
       <c r="E15" s="9">
-        <v>6.2346891401811107E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B16" s="14">
-        <v>5.5416408703768489</v>
+        <v>1.3792929570580797E-2</v>
+      </c>
+      <c r="H15" s="35"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="37" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="3">
+        <v>4.4625041854104465E-2</v>
       </c>
       <c r="C16" s="10">
         <v>4763.4799999999996</v>
@@ -2667,15 +3015,20 @@
         <v>9.8175096591700992</v>
       </c>
       <c r="E16" s="9">
-        <v>4.5743624529648579E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="B17" s="14">
-        <v>6.9279062373845104</v>
+        <v>9.3681598020994034E-3</v>
+      </c>
+      <c r="H16" s="35"/>
+      <c r="L16" s="32"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="B17" s="3">
+        <v>7.2771809148887978E-2</v>
       </c>
       <c r="C17" s="10">
         <v>6984.73</v>
@@ -2684,15 +3037,20 @@
         <v>97.838490831037788</v>
       </c>
       <c r="E17" s="9">
-        <v>3.4358171286213941E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" s="14">
-        <v>9.7129209151631191</v>
+        <v>1.0418700386255158E-2</v>
+      </c>
+      <c r="H17" s="35"/>
+      <c r="L17" s="32"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="3">
+        <v>6.6472857650629213E-2</v>
       </c>
       <c r="C18" s="10">
         <v>5458.94</v>
@@ -2701,15 +3059,20 @@
         <v>56.440766055090855</v>
       </c>
       <c r="E18" s="9">
-        <v>7.224852578947713E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="14">
-        <v>2.4079595436642505</v>
+        <v>1.2176880062911339E-2</v>
+      </c>
+      <c r="H18" s="35"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="37" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="3">
+        <v>2.5579799677679687E-2</v>
       </c>
       <c r="C19" s="10">
         <v>3774.29</v>
@@ -2718,15 +3081,20 @@
         <v>2.0791554895781785</v>
       </c>
       <c r="E19" s="9">
-        <v>2.5553439402960784E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B20" s="14">
-        <v>9.2637572206152026</v>
+        <v>6.7773805610272884E-3</v>
+      </c>
+      <c r="H19" s="35"/>
+      <c r="L19" s="32"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="37" t="s">
+        <v>42</v>
+      </c>
+      <c r="B20" s="3">
+        <v>4.6111652524633229E-2</v>
       </c>
       <c r="C20" s="10">
         <v>5825.61</v>
@@ -2735,16 +3103,20 @@
         <v>84.589009893810285</v>
       </c>
       <c r="E20" s="9">
-        <v>5.84495027314385E-2</v>
-      </c>
-      <c r="H20" s="19"/>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="B21" s="14">
-        <v>7.0846322868217886</v>
+        <v>7.9153346215474832E-3</v>
+      </c>
+      <c r="H20" s="35"/>
+      <c r="L20" s="32"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="3">
+        <v>7.2895017655790845E-2</v>
       </c>
       <c r="C21" s="10">
         <v>3578.39</v>
@@ -2753,15 +3125,20 @@
         <v>84.863671420146076</v>
       </c>
       <c r="E21" s="9">
-        <v>7.3293646203890422E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="B22" s="14">
-        <v>1.2107377461739792</v>
+        <v>2.0370897989260769E-2</v>
+      </c>
+      <c r="H21" s="35"/>
+      <c r="L21" s="32"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="3">
+        <v>1.0005187914025705E-2</v>
       </c>
       <c r="C22" s="10">
         <v>693.89</v>
@@ -2770,15 +3147,20 @@
         <v>95.801510788364425</v>
       </c>
       <c r="E22" s="9">
-        <v>6.0213086629161867E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="B23" s="14">
-        <v>0.27446771050253921</v>
+        <v>1.4418982711994271E-2</v>
+      </c>
+      <c r="H22" s="35"/>
+      <c r="L22" s="32"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="37" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="3">
+        <v>5.7301854941079131E-3</v>
       </c>
       <c r="C23" s="10">
         <v>304.89999999999998</v>
@@ -2787,15 +3169,20 @@
         <v>100</v>
       </c>
       <c r="E23" s="9">
-        <v>3.1202013191000043E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="14">
-        <v>6.0624115740718381</v>
+        <v>1.8793655277493975E-2</v>
+      </c>
+      <c r="H23" s="35"/>
+      <c r="L23" s="32"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="B24" s="3">
+        <v>5.1357443720254699E-2</v>
       </c>
       <c r="C24" s="10">
         <v>3022.97</v>
@@ -2804,35 +3191,42 @@
         <v>95.332076039702144</v>
       </c>
       <c r="E24" s="9">
-        <v>6.9589159176085755E-2</v>
-      </c>
-      <c r="J24" s="19"/>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="B25" s="14">
-        <v>14.390716794265884</v>
+        <v>1.6989068274000308E-2</v>
+      </c>
+      <c r="H24" s="35"/>
+      <c r="L24" s="32"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0.16764936817540885</v>
       </c>
       <c r="C25" s="10">
         <v>8387.9</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="30">
         <v>98.735941874099751</v>
       </c>
       <c r="E25" s="9">
-        <v>5.6108345552395432E-2</v>
-      </c>
-      <c r="I25" s="19"/>
-      <c r="N25" s="19"/>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="B26" s="14">
-        <v>0.23026438443707109</v>
+        <v>1.9987048984299868E-2</v>
+      </c>
+      <c r="H25" s="35"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1.8589723827653292E-3</v>
       </c>
       <c r="C26" s="10">
         <v>127.17</v>
@@ -2841,17 +3235,20 @@
         <v>15.683581124757598</v>
       </c>
       <c r="E26" s="9">
-        <v>7.6766153139745108E-2</v>
-      </c>
-      <c r="J26" s="19"/>
-      <c r="K26" s="19"/>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="B27" s="14">
-        <v>3.3118990645121906</v>
+        <v>1.4618010401551697E-2</v>
+      </c>
+      <c r="H26" s="35"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" s="3">
+        <v>3.9980616112343978E-2</v>
       </c>
       <c r="C27" s="10">
         <v>3160.96</v>
@@ -2860,15 +3257,20 @@
         <v>99.90715417029017</v>
       </c>
       <c r="E27" s="9">
-        <v>3.4996612384486488E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B28" s="14">
-        <v>7.8108987202422897</v>
+        <v>1.2648251199744377E-2</v>
+      </c>
+      <c r="H27" s="35"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="10"/>
+      <c r="N27" s="10"/>
+      <c r="O27" s="10"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" s="3">
+        <v>2.9105964022045114E-2</v>
       </c>
       <c r="C28" s="10">
         <v>6403.97</v>
@@ -2877,15 +3279,20 @@
         <v>57.130244877096793</v>
       </c>
       <c r="E28" s="9">
-        <v>4.7316221693710997E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="B29" s="14">
-        <v>0.59565338398593981</v>
+        <v>4.5449875658451107E-3</v>
+      </c>
+      <c r="H28" s="35"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="10"/>
+      <c r="N28" s="10"/>
+      <c r="O28" s="10"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="38" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="3">
+        <v>4.2035061455769872E-3</v>
       </c>
       <c r="C29" s="10">
         <v>390.03</v>
@@ -2894,53 +3301,64 @@
         <v>85.469394355947287</v>
       </c>
       <c r="E29" s="9">
-        <v>5.2816538454256573E-2</v>
-      </c>
-      <c r="J29" s="19"/>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="14">
-        <v>0.11071966003784414</v>
+        <v>1.0777391855952076E-2</v>
+      </c>
+      <c r="H29" s="35"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="10"/>
+      <c r="N29" s="10"/>
+      <c r="O29" s="10"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="3">
+        <v>5.8570693039903206E-2</v>
       </c>
       <c r="C30" s="10">
-        <v>194.58</v>
+        <v>2824.76</v>
       </c>
       <c r="D30" s="10">
         <v>97.779499096307774</v>
       </c>
       <c r="E30" s="9">
-        <v>2.906919889132821E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B31" s="14">
-        <v>5.9011102851911836</v>
-      </c>
-      <c r="C31" s="10">
-        <v>2824.76</v>
-      </c>
-      <c r="D31" s="21">
+        <v>2.073475022299353E-2</v>
+      </c>
+      <c r="H30" s="35"/>
+      <c r="L30" s="32"/>
+      <c r="M30" s="10"/>
+      <c r="N30" s="10"/>
+      <c r="O30" s="10"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="3">
+        <v>1.0227709498898587E-2</v>
+      </c>
+      <c r="C31" s="12">
+        <v>194.58</v>
+      </c>
+      <c r="D31" s="30">
         <v>98.524118472527761</v>
       </c>
       <c r="E31" s="9">
-        <v>7.2853127528349354E-2</v>
-      </c>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-      <c r="N31" s="19"/>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="B32" s="14">
-        <v>5.0590173256264865</v>
+        <v>5.2563004928042896E-2</v>
+      </c>
+      <c r="H31" s="35"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="10"/>
+      <c r="N31" s="10"/>
+      <c r="O31" s="10"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="3">
+        <v>3.1193450689785095E-2</v>
       </c>
       <c r="C32" s="10">
         <v>4243.22</v>
@@ -2949,15 +3367,20 @@
         <v>76.298746324957008</v>
       </c>
       <c r="E32" s="9">
-        <v>4.0808764172001348E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="B33" s="14">
-        <v>2.1612952589328684</v>
+        <v>7.351363042638631E-3</v>
+      </c>
+      <c r="H32" s="35"/>
+      <c r="L32" s="32"/>
+      <c r="M32" s="10"/>
+      <c r="N32" s="10"/>
+      <c r="O32" s="10"/>
+    </row>
+    <row r="33" spans="1:33">
+      <c r="A33" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="3">
+        <v>1.2660608447709169E-2</v>
       </c>
       <c r="C33" s="10">
         <v>1024.68</v>
@@ -2966,10 +3389,330 @@
         <v>21.770995310936726</v>
       </c>
       <c r="E33" s="9">
-        <v>8.55869802447696E-2</v>
-      </c>
+        <v>1.2355670499774726E-2</v>
+      </c>
+      <c r="H33" s="35"/>
+      <c r="L33" s="32"/>
+      <c r="M33" s="10"/>
+      <c r="N33" s="10"/>
+      <c r="O33" s="10"/>
+    </row>
+    <row r="37" spans="1:33" s="35" customFormat="1"/>
+    <row r="38" spans="1:33" s="35" customFormat="1"/>
+    <row r="39" spans="1:33" s="35" customFormat="1"/>
+    <row r="40" spans="1:33" s="35" customFormat="1"/>
+    <row r="41" spans="1:33" s="35" customFormat="1"/>
+    <row r="42" spans="1:33" s="35" customFormat="1"/>
+    <row r="43" spans="1:33" s="35" customFormat="1"/>
+    <row r="44" spans="1:33" s="35" customFormat="1"/>
+    <row r="45" spans="1:33" s="35" customFormat="1"/>
+    <row r="46" spans="1:33" s="35" customFormat="1"/>
+    <row r="47" spans="1:33" s="35" customFormat="1"/>
+    <row r="48" spans="1:33">
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
+      <c r="L48" s="10"/>
+      <c r="M48" s="10"/>
+      <c r="N48" s="10"/>
+      <c r="O48" s="10"/>
+      <c r="P48" s="10"/>
+      <c r="Q48" s="10"/>
+      <c r="R48" s="10"/>
+      <c r="S48" s="10"/>
+      <c r="T48" s="10"/>
+      <c r="U48" s="10"/>
+      <c r="V48" s="10"/>
+      <c r="W48" s="10"/>
+      <c r="X48" s="10"/>
+      <c r="Y48" s="10"/>
+      <c r="Z48" s="10"/>
+      <c r="AA48" s="10"/>
+      <c r="AB48" s="10"/>
+      <c r="AC48" s="10"/>
+      <c r="AD48" s="10"/>
+      <c r="AE48" s="10"/>
+      <c r="AF48" s="10"/>
+      <c r="AG48" s="10"/>
+    </row>
+    <row r="49" spans="1:33">
+      <c r="F49" s="10"/>
+      <c r="G49" s="10"/>
+      <c r="H49" s="10"/>
+      <c r="I49" s="10"/>
+      <c r="J49" s="10"/>
+      <c r="K49" s="10"/>
+      <c r="L49" s="10"/>
+      <c r="M49" s="10"/>
+      <c r="N49" s="10"/>
+      <c r="O49" s="10"/>
+      <c r="P49" s="10"/>
+      <c r="Q49" s="10"/>
+      <c r="R49" s="10"/>
+      <c r="S49" s="10"/>
+      <c r="T49" s="10"/>
+      <c r="U49" s="10"/>
+      <c r="V49" s="10"/>
+      <c r="W49" s="10"/>
+      <c r="X49" s="10"/>
+      <c r="Y49" s="10"/>
+      <c r="Z49" s="10"/>
+      <c r="AA49" s="10"/>
+      <c r="AB49" s="10"/>
+      <c r="AC49" s="10"/>
+      <c r="AD49" s="10"/>
+      <c r="AE49" s="10"/>
+      <c r="AF49" s="10"/>
+      <c r="AG49" s="10"/>
+    </row>
+    <row r="50" spans="1:33">
+      <c r="F50" s="10"/>
+      <c r="G50" s="10"/>
+      <c r="H50" s="10"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="10"/>
+      <c r="K50" s="10"/>
+      <c r="L50" s="10"/>
+      <c r="M50" s="10"/>
+      <c r="N50" s="10"/>
+      <c r="O50" s="10"/>
+      <c r="P50" s="10"/>
+      <c r="Q50" s="10"/>
+      <c r="R50" s="10"/>
+      <c r="S50" s="10"/>
+      <c r="T50" s="10"/>
+      <c r="U50" s="10"/>
+      <c r="V50" s="10"/>
+      <c r="W50" s="10"/>
+      <c r="X50" s="10"/>
+      <c r="Y50" s="10"/>
+      <c r="Z50" s="10"/>
+      <c r="AA50" s="10"/>
+      <c r="AB50" s="10"/>
+      <c r="AC50" s="10"/>
+      <c r="AD50" s="10"/>
+      <c r="AE50" s="10"/>
+      <c r="AF50" s="10"/>
+      <c r="AG50" s="10"/>
+    </row>
+    <row r="51" spans="1:33">
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
+      <c r="K51" s="10"/>
+      <c r="L51" s="10"/>
+      <c r="M51" s="10"/>
+      <c r="N51" s="10"/>
+      <c r="O51" s="10"/>
+      <c r="P51" s="10"/>
+      <c r="Q51" s="10"/>
+      <c r="R51" s="10"/>
+      <c r="S51" s="10"/>
+      <c r="T51" s="10"/>
+      <c r="U51" s="10"/>
+      <c r="V51" s="10"/>
+      <c r="W51" s="10"/>
+      <c r="X51" s="10"/>
+      <c r="Y51" s="10"/>
+      <c r="Z51" s="10"/>
+      <c r="AA51" s="10"/>
+      <c r="AB51" s="10"/>
+      <c r="AC51" s="10"/>
+      <c r="AD51" s="10"/>
+      <c r="AE51" s="10"/>
+      <c r="AF51" s="10"/>
+      <c r="AG51" s="10"/>
+    </row>
+    <row r="52" spans="1:33">
+      <c r="F52" s="10"/>
+      <c r="G52" s="10"/>
+      <c r="H52" s="10"/>
+      <c r="I52" s="10"/>
+      <c r="J52" s="10"/>
+      <c r="K52" s="10"/>
+      <c r="L52" s="10"/>
+      <c r="M52" s="10"/>
+      <c r="N52" s="10"/>
+      <c r="O52" s="10"/>
+      <c r="P52" s="10"/>
+      <c r="Q52" s="10"/>
+      <c r="R52" s="10"/>
+      <c r="S52" s="10"/>
+      <c r="T52" s="10"/>
+      <c r="U52" s="10"/>
+      <c r="V52" s="10"/>
+      <c r="W52" s="10"/>
+      <c r="X52" s="10"/>
+      <c r="Y52" s="10"/>
+      <c r="Z52" s="10"/>
+      <c r="AA52" s="10"/>
+      <c r="AB52" s="10"/>
+      <c r="AC52" s="10"/>
+      <c r="AD52" s="10"/>
+      <c r="AE52" s="10"/>
+      <c r="AF52" s="10"/>
+      <c r="AG52" s="10"/>
+    </row>
+    <row r="53" spans="1:33">
+      <c r="F53" s="10"/>
+      <c r="G53" s="10"/>
+      <c r="H53" s="10"/>
+      <c r="I53" s="10"/>
+      <c r="J53" s="10"/>
+      <c r="K53" s="10"/>
+      <c r="L53" s="10"/>
+      <c r="M53" s="10"/>
+      <c r="N53" s="10"/>
+      <c r="O53" s="10"/>
+      <c r="P53" s="10"/>
+      <c r="Q53" s="10"/>
+      <c r="R53" s="10"/>
+      <c r="S53" s="10"/>
+      <c r="T53" s="10"/>
+      <c r="U53" s="10"/>
+      <c r="V53" s="10"/>
+      <c r="W53" s="10"/>
+      <c r="X53" s="10"/>
+      <c r="Y53" s="10"/>
+      <c r="Z53" s="10"/>
+      <c r="AA53" s="10"/>
+      <c r="AB53" s="10"/>
+      <c r="AC53" s="10"/>
+      <c r="AD53" s="10"/>
+      <c r="AE53" s="10"/>
+      <c r="AF53" s="10"/>
+    </row>
+    <row r="54" spans="1:33">
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="10"/>
+      <c r="K54" s="10"/>
+      <c r="L54" s="10"/>
+      <c r="M54" s="10"/>
+      <c r="N54" s="10"/>
+      <c r="O54" s="10"/>
+      <c r="P54" s="10"/>
+      <c r="Q54" s="10"/>
+      <c r="R54" s="10"/>
+      <c r="S54" s="10"/>
+      <c r="T54" s="10"/>
+      <c r="U54" s="10"/>
+      <c r="V54" s="10"/>
+      <c r="W54" s="10"/>
+      <c r="X54" s="10"/>
+      <c r="Y54" s="10"/>
+      <c r="Z54" s="10"/>
+      <c r="AA54" s="10"/>
+      <c r="AB54" s="10"/>
+      <c r="AC54" s="10"/>
+      <c r="AD54" s="10"/>
+      <c r="AE54" s="10"/>
+      <c r="AF54" s="10"/>
+    </row>
+    <row r="55" spans="1:33">
+      <c r="A55" s="35"/>
+    </row>
+    <row r="56" spans="1:33">
+      <c r="A56" s="35"/>
+    </row>
+    <row r="57" spans="1:33">
+      <c r="A57" s="35"/>
+    </row>
+    <row r="58" spans="1:33">
+      <c r="A58" s="35"/>
+    </row>
+    <row r="59" spans="1:33">
+      <c r="A59" s="35"/>
+    </row>
+    <row r="60" spans="1:33">
+      <c r="A60" s="35"/>
+    </row>
+    <row r="61" spans="1:33">
+      <c r="A61" s="35"/>
+    </row>
+    <row r="62" spans="1:33">
+      <c r="A62" s="35"/>
+    </row>
+    <row r="63" spans="1:33">
+      <c r="A63" s="35"/>
+    </row>
+    <row r="64" spans="1:33">
+      <c r="A64" s="35"/>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="35"/>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="35"/>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="35"/>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="35"/>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="35"/>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="35"/>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="35"/>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="35"/>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="35"/>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="35"/>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="35"/>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="35"/>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="35"/>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="35"/>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="35"/>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="35"/>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="35"/>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="35"/>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="35"/>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="35"/>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="35"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H3:K33">
+    <sortCondition ref="H3:H33"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -2995,13 +3738,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>4</v>
@@ -3012,51 +3755,51 @@
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>106</v>
-      </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="32" t="s">
         <v>7</v>
       </c>
       <c r="B3">
-        <v>39.918020495417267</v>
-      </c>
-      <c r="C3" s="4">
+        <v>1.136873169064325</v>
+      </c>
+      <c r="C3" s="10">
         <v>7334.46</v>
       </c>
       <c r="D3" s="4">
         <v>61.955119427962899</v>
       </c>
       <c r="E3" s="5">
-        <v>1.6642456517978684E-2</v>
+        <v>0.15500434511393138</v>
       </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="4" t="s">
-        <v>9</v>
+      <c r="A4" s="31" t="s">
+        <v>122</v>
       </c>
       <c r="B4">
-        <v>5.7883733533298026E-4</v>
-      </c>
-      <c r="C4" s="4">
+        <v>2.4384246342857144E-6</v>
+      </c>
+      <c r="C4" s="10">
         <v>89.47</v>
       </c>
       <c r="D4" s="7">
         <v>99.594893199116129</v>
       </c>
       <c r="E4" s="5">
-        <v>2.0364789799288402E-4</v>
+        <v>2.725410343451117E-5</v>
       </c>
       <c r="F4"/>
       <c r="H4" s="8"/>
@@ -3065,342 +3808,342 @@
       <c r="N4" s="8"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
+      <c r="A5" s="32" t="s">
+        <v>10</v>
       </c>
       <c r="B5">
-        <v>7.2826396719761552</v>
-      </c>
-      <c r="C5" s="4">
+        <v>0.20768459556555752</v>
+      </c>
+      <c r="C5" s="10">
         <v>2025.93</v>
       </c>
       <c r="D5" s="4">
         <v>41.559481240326626</v>
       </c>
       <c r="E5" s="5">
-        <v>1.2996013280329047E-2</v>
+        <v>0.10251321396373889</v>
       </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>13</v>
+      <c r="A6" s="32" t="s">
+        <v>12</v>
       </c>
       <c r="B6">
-        <v>4.9011241717636702</v>
-      </c>
-      <c r="C6" s="4">
+        <v>0.13988200128459069</v>
+      </c>
+      <c r="C6" s="10">
         <v>841.1</v>
       </c>
       <c r="D6" s="4">
         <v>5.6727238489784382</v>
       </c>
       <c r="E6" s="5">
-        <v>2.0615231006712722E-2</v>
+        <v>0.16630840718653037</v>
       </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="4" t="s">
-        <v>15</v>
+      <c r="A7" s="32" t="s">
+        <v>16</v>
       </c>
       <c r="B7">
-        <v>1.7343953636444621E-2</v>
-      </c>
-      <c r="C7" s="4">
+        <v>0.56785028858304287</v>
+      </c>
+      <c r="C7" s="10">
         <v>2710.93</v>
       </c>
       <c r="D7" s="4">
         <v>99.87565228251367</v>
       </c>
       <c r="E7" s="5">
-        <v>5.3046084546547253E-5</v>
+        <v>0.20946696837728859</v>
       </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="4" t="s">
-        <v>17</v>
+      <c r="A8" s="32" t="s">
+        <v>14</v>
       </c>
       <c r="B8">
-        <v>19.833170470785301</v>
-      </c>
-      <c r="C8" s="4">
+        <v>1.2489348178223859E-4</v>
+      </c>
+      <c r="C8" s="10">
         <v>2229.5100000000002</v>
       </c>
       <c r="D8" s="4">
         <v>6.8638842174998729</v>
       </c>
       <c r="E8" s="5">
-        <v>2.0782164146623459E-2</v>
+        <v>5.6018354608070187E-5</v>
       </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="4" t="s">
-        <v>19</v>
+      <c r="A9" s="32" t="s">
+        <v>18</v>
       </c>
       <c r="B9">
-        <v>17.733690784992106</v>
-      </c>
-      <c r="C9" s="4">
+        <v>0.50631971903816431</v>
+      </c>
+      <c r="C9" s="10">
         <v>2834.72</v>
       </c>
       <c r="D9" s="4">
         <v>26.076880447377697</v>
       </c>
       <c r="E9" s="5">
-        <v>1.9331043260294122E-2</v>
+        <v>0.17861366168022391</v>
       </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="4" t="s">
-        <v>21</v>
+      <c r="A10" s="32" t="s">
+        <v>20</v>
       </c>
       <c r="B10">
-        <v>6.0158338481056068</v>
-      </c>
-      <c r="C10" s="4">
+        <v>0.1711944996629875</v>
+      </c>
+      <c r="C10" s="10">
         <v>2773.8</v>
       </c>
       <c r="D10" s="4">
         <v>58.164277276240753</v>
       </c>
       <c r="E10" s="5">
-        <v>1.1070543991455952E-2</v>
+        <v>6.1718400628375331E-2</v>
       </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="4" t="s">
-        <v>23</v>
+      <c r="A11" s="32" t="s">
+        <v>22</v>
       </c>
       <c r="B11">
-        <v>2.38022410055058</v>
-      </c>
-      <c r="C11" s="4">
+        <v>6.8287809615252146E-2</v>
+      </c>
+      <c r="C11" s="10">
         <v>273.58999999999997</v>
       </c>
       <c r="D11" s="4">
         <v>0</v>
       </c>
       <c r="E11" s="5">
-        <v>2.2378968270983547E-2</v>
+        <v>0.24959907019720073</v>
       </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="4" t="s">
-        <v>25</v>
+      <c r="A12" s="32" t="s">
+        <v>24</v>
       </c>
       <c r="B12">
-        <v>7.5340405456350387E-2</v>
-      </c>
-      <c r="C12" s="4">
+        <v>7.5873937931161079E-5</v>
+      </c>
+      <c r="C12" s="10">
         <v>6455.19</v>
       </c>
       <c r="D12" s="4">
         <v>98.724884616719294</v>
       </c>
       <c r="E12" s="5">
-        <v>5.6875408395013524E-4</v>
+        <v>1.1753943405408839E-5</v>
       </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="4" t="s">
-        <v>27</v>
+      <c r="A13" s="32" t="s">
+        <v>28</v>
       </c>
       <c r="B13">
-        <v>73.90093776778059</v>
-      </c>
-      <c r="C13" s="4">
+        <v>0.25135037722419712</v>
+      </c>
+      <c r="C13" s="10">
         <v>14743.09</v>
       </c>
       <c r="D13" s="7">
         <v>66.440509510716112</v>
       </c>
       <c r="E13" s="5">
-        <v>1.2254361215148158E-2</v>
+        <v>1.7048690418643386E-2</v>
       </c>
       <c r="F13"/>
       <c r="I13" s="8"/>
       <c r="N13" s="8"/>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="4" t="s">
-        <v>29</v>
+      <c r="A14" s="32" t="s">
+        <v>26</v>
       </c>
       <c r="B14">
-        <v>8.8652740457638792</v>
-      </c>
-      <c r="C14" s="4">
+        <v>2.1086877574096574</v>
+      </c>
+      <c r="C14" s="10">
         <v>10785.29</v>
       </c>
       <c r="D14" s="4">
         <v>94.174746750627875</v>
       </c>
       <c r="E14" s="5">
-        <v>2.2465872478839174E-3</v>
+        <v>0.19551516532329286</v>
       </c>
       <c r="F14"/>
       <c r="H14" s="8"/>
       <c r="J14" s="8"/>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="4" t="s">
-        <v>31</v>
+      <c r="A15" s="31" t="s">
+        <v>30</v>
       </c>
       <c r="B15">
-        <v>33.83864204219973</v>
-      </c>
-      <c r="C15" s="4">
+        <v>0.96016861820538568</v>
+      </c>
+      <c r="C15" s="10">
         <v>4706.97</v>
       </c>
       <c r="D15" s="4">
         <v>44.231396446656937</v>
       </c>
       <c r="E15" s="5">
-        <v>2.2572490356442824E-2</v>
+        <v>0.20398868448394308</v>
       </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="4" t="s">
-        <v>33</v>
+      <c r="A16" s="32" t="s">
+        <v>32</v>
       </c>
       <c r="B16">
-        <v>38.85324368788558</v>
-      </c>
-      <c r="C16" s="4">
+        <v>1.1105471354913357</v>
+      </c>
+      <c r="C16" s="10">
         <v>4763.4799999999996</v>
       </c>
       <c r="D16" s="4">
         <v>9.8175096591700992</v>
       </c>
       <c r="E16" s="5">
-        <v>2.0816584563956114E-2</v>
+        <v>0.23313777647672201</v>
       </c>
       <c r="F16"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="4" t="s">
-        <v>35</v>
+      <c r="A17" s="32" t="s">
+        <v>40</v>
       </c>
       <c r="B17">
-        <v>2.9733722623491472</v>
-      </c>
-      <c r="C17" s="4">
+        <v>0.4476716684818714</v>
+      </c>
+      <c r="C17" s="10">
         <v>6984.73</v>
       </c>
       <c r="D17" s="4">
         <v>97.838490831037788</v>
       </c>
       <c r="E17" s="5">
-        <v>7.7047479744542452E-4</v>
+        <v>6.4092909601641226E-2</v>
       </c>
       <c r="F17"/>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="4" t="s">
-        <v>37</v>
+      <c r="A18" s="32" t="s">
+        <v>36</v>
       </c>
       <c r="B18">
-        <v>37.442185413879855</v>
-      </c>
-      <c r="C18" s="4">
+        <v>1.065444247972718</v>
+      </c>
+      <c r="C18" s="10">
         <v>5458.94</v>
       </c>
       <c r="D18" s="4">
         <v>56.440766055090855</v>
       </c>
       <c r="E18" s="5">
-        <v>1.4409848523620195E-2</v>
+        <v>0.19517420011443942</v>
       </c>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="4" t="s">
-        <v>39</v>
+      <c r="A19" s="32" t="s">
+        <v>38</v>
       </c>
       <c r="B19">
-        <v>36.964930503449203</v>
-      </c>
-      <c r="C19" s="4">
+        <v>1.0549722350305142</v>
+      </c>
+      <c r="C19" s="10">
         <v>3774.29</v>
       </c>
       <c r="D19" s="4">
         <v>2.0791554895781785</v>
       </c>
       <c r="E19" s="5">
-        <v>2.5914794888235053E-2</v>
+        <v>0.27951541482782566</v>
       </c>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="4" t="s">
-        <v>41</v>
+      <c r="A20" s="32" t="s">
+        <v>42</v>
       </c>
       <c r="B20">
-        <v>15.695353276908648</v>
-      </c>
-      <c r="C20" s="4">
+        <v>0.25319743390939392</v>
+      </c>
+      <c r="C20" s="10">
         <v>5825.61</v>
       </c>
       <c r="D20" s="4">
         <v>84.589009893810285</v>
       </c>
       <c r="E20" s="5">
-        <v>5.7807503101921908E-3</v>
+        <v>4.3462819157031443E-2</v>
       </c>
       <c r="F20"/>
       <c r="H20" s="8"/>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="4" t="s">
-        <v>43</v>
+      <c r="A21" s="32" t="s">
+        <v>34</v>
       </c>
       <c r="B21">
-        <v>8.9160895512490157</v>
-      </c>
-      <c r="C21" s="4">
+        <v>8.2532666393003579E-2</v>
+      </c>
+      <c r="C21" s="10">
         <v>3578.39</v>
       </c>
       <c r="D21" s="4">
         <v>84.863671420146076</v>
       </c>
       <c r="E21" s="5">
-        <v>5.7006985448150096E-3</v>
+        <v>2.3064189871144166E-2</v>
       </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="4" t="s">
-        <v>45</v>
+      <c r="A22" s="32" t="s">
+        <v>44</v>
       </c>
       <c r="B22">
-        <v>1.06772510064468</v>
-      </c>
-      <c r="C22" s="4">
+        <v>3.047379517084543E-2</v>
+      </c>
+      <c r="C22" s="10">
         <v>693.89</v>
       </c>
       <c r="D22" s="4">
         <v>95.801510788364425</v>
       </c>
       <c r="E22" s="5">
-        <v>1.5661384188500529E-3</v>
+        <v>4.391732864120456E-2</v>
       </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="4" t="s">
-        <v>47</v>
+      <c r="A23" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="B23">
-        <v>6.806067710778879E-4</v>
-      </c>
-      <c r="C23" s="4">
+        <v>0</v>
+      </c>
+      <c r="C23" s="10">
         <v>304.89999999999998</v>
       </c>
       <c r="D23" s="4">
@@ -3412,152 +4155,152 @@
       <c r="F23"/>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="4" t="s">
-        <v>49</v>
+      <c r="A24" s="32" t="s">
+        <v>56</v>
       </c>
       <c r="B24">
-        <v>1.1239091946725712</v>
-      </c>
-      <c r="C24" s="4">
+        <v>0.6362406729521678</v>
+      </c>
+      <c r="C24" s="10">
         <v>3022.97</v>
       </c>
       <c r="D24" s="4">
         <v>95.332076039702144</v>
       </c>
       <c r="E24" s="5">
-        <v>2.3487732360310048E-3</v>
+        <v>0.21046873536692981</v>
       </c>
       <c r="F24"/>
       <c r="J24" s="8"/>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="4" t="s">
-        <v>51</v>
+      <c r="A25" s="32" t="s">
+        <v>50</v>
       </c>
       <c r="B25">
-        <v>1.8360533695986589</v>
-      </c>
-      <c r="C25" s="4">
+        <v>4.9005040410684285E-2</v>
+      </c>
+      <c r="C25" s="10">
         <v>8387.9</v>
       </c>
       <c r="D25" s="7">
         <v>98.735941874099751</v>
       </c>
       <c r="E25" s="5">
-        <v>4.4995371677144212E-4</v>
+        <v>5.8423491470671182E-3</v>
       </c>
       <c r="F25"/>
       <c r="I25" s="8"/>
       <c r="N25" s="8"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="4" t="s">
-        <v>53</v>
+      <c r="A26" s="32" t="s">
+        <v>52</v>
       </c>
       <c r="B26">
-        <v>1.1876835400045826</v>
-      </c>
-      <c r="C26" s="4">
+        <v>3.7447283077384645E-2</v>
+      </c>
+      <c r="C26" s="10">
         <v>127.17</v>
       </c>
       <c r="D26" s="4">
         <v>15.683581124757598</v>
       </c>
       <c r="E26" s="5">
-        <v>2.5241571061231094E-2</v>
+        <v>0.29446632914511794</v>
       </c>
       <c r="F26"/>
       <c r="J26" s="8"/>
       <c r="K26" s="8"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="4" t="s">
-        <v>55</v>
+      <c r="A27" s="32" t="s">
+        <v>48</v>
       </c>
       <c r="B27">
-        <v>2.2110723319606358E-2</v>
-      </c>
-      <c r="C27" s="4">
+        <v>3.1342503602080254E-2</v>
+      </c>
+      <c r="C27" s="10">
         <v>3160.96</v>
       </c>
       <c r="D27" s="4">
         <v>99.90715417029017</v>
       </c>
       <c r="E27" s="5">
-        <v>4.4086287875366175E-5</v>
+        <v>9.9155014938753575E-3</v>
       </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="4" t="s">
-        <v>57</v>
+      <c r="A28" s="32" t="s">
+        <v>54</v>
       </c>
       <c r="B28">
-        <v>22.352009297583415</v>
-      </c>
-      <c r="C28" s="4">
+        <v>1.6568510315763501E-5</v>
+      </c>
+      <c r="C28" s="10">
         <v>6403.97</v>
       </c>
       <c r="D28" s="4">
         <v>57.130244877096793</v>
       </c>
       <c r="E28" s="5">
-        <v>1.1093404229110457E-2</v>
+        <v>2.5872248489239485E-6</v>
       </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="4" t="s">
-        <v>59</v>
+      <c r="A29" s="31" t="s">
+        <v>58</v>
       </c>
       <c r="B29">
-        <v>4.2180261896406085E-3</v>
-      </c>
-      <c r="C29" s="4">
+        <v>4.2516416071428573E-3</v>
+      </c>
+      <c r="C29" s="10">
         <v>390.03</v>
       </c>
       <c r="D29" s="4">
         <v>85.469394355947287</v>
       </c>
       <c r="E29" s="5">
-        <v>6.2158394788828049E-3</v>
+        <v>1.0900806622933768E-2</v>
       </c>
       <c r="F29"/>
       <c r="J29" s="8"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="4" t="s">
-        <v>61</v>
+      <c r="A30" s="32" t="s">
+        <v>62</v>
       </c>
       <c r="B30">
-        <v>1.599087481408539E-4</v>
-      </c>
-      <c r="C30" s="4">
-        <v>194.58</v>
+        <v>0</v>
+      </c>
+      <c r="C30" s="10">
+        <v>2824.76</v>
       </c>
       <c r="D30" s="4">
         <v>97.779499096307774</v>
       </c>
       <c r="E30" s="5">
-        <v>1.2801014450261781E-4</v>
+        <v>0</v>
       </c>
       <c r="F30"/>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="4" t="s">
-        <v>63</v>
+      <c r="A31" s="32" t="s">
+        <v>60</v>
       </c>
       <c r="B31">
-        <v>1.2190739558232137E-2</v>
-      </c>
-      <c r="C31" s="4">
-        <v>2824.76</v>
+        <v>1.2691557864392429E-6</v>
+      </c>
+      <c r="C31" s="12">
+        <v>194.58</v>
       </c>
       <c r="D31" s="7">
         <v>98.524118472527761</v>
       </c>
       <c r="E31" s="5">
-        <v>5.5168551468058092E-4</v>
+        <v>6.52253975968364E-6</v>
       </c>
       <c r="F31"/>
       <c r="I31" s="8"/>
@@ -3565,38 +4308,38 @@
       <c r="N31" s="8"/>
     </row>
     <row r="32" spans="1:14">
-      <c r="A32" s="4" t="s">
-        <v>65</v>
+      <c r="A32" s="32" t="s">
+        <v>64</v>
       </c>
       <c r="B32">
-        <v>6.6471188987390253</v>
-      </c>
-      <c r="C32" s="4">
+        <v>0.18832402782523466</v>
+      </c>
+      <c r="C32" s="10">
         <v>4243.22</v>
       </c>
       <c r="D32" s="4">
         <v>76.298746324957008</v>
       </c>
       <c r="E32" s="5">
-        <v>7.4823509540297862E-3</v>
+        <v>4.4382338842962332E-2</v>
       </c>
       <c r="F32"/>
     </row>
     <row r="33" spans="1:6">
-      <c r="A33" s="4" t="s">
-        <v>67</v>
+      <c r="A33" s="32" t="s">
+        <v>66</v>
       </c>
       <c r="B33">
-        <v>6.8359483357800439</v>
-      </c>
-      <c r="C33" s="4">
+        <v>0.19515889852438645</v>
+      </c>
+      <c r="C33" s="10">
         <v>1024.68</v>
       </c>
       <c r="D33" s="4">
         <v>21.770995310936726</v>
       </c>
       <c r="E33" s="5">
-        <v>2.0692839067026722E-2</v>
+        <v>0.19045838556855454</v>
       </c>
       <c r="F33"/>
     </row>
@@ -3611,7 +4354,11 @@
   <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="16384" width="10.83203125" style="11"/>
+    <col min="1" max="2" width="10.83203125" style="11"/>
+    <col min="3" max="3" width="24" style="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.6640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.33203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="10.83203125" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3619,13 +4366,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E1" s="11" t="s">
         <v>4</v>
@@ -3636,546 +4383,580 @@
         <v>5</v>
       </c>
       <c r="B2" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>106</v>
-      </c>
     </row>
     <row r="3" spans="1:5">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="32" t="s">
         <v>7</v>
       </c>
       <c r="B3">
-        <v>18.064235568014361</v>
-      </c>
-      <c r="C3" s="11">
+        <v>0.344508706224401</v>
+      </c>
+      <c r="C3" s="10">
         <v>7334.46</v>
       </c>
       <c r="D3" s="11">
         <v>61.955119427962899</v>
       </c>
       <c r="E3" s="11">
-        <v>0.24679882850061927</v>
+        <f>B3*1000000/C3/1000</f>
+        <v>4.6971243448652118E-2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
-      <c r="A4" s="11" t="s">
-        <v>9</v>
+      <c r="A4" s="31" t="s">
+        <v>122</v>
       </c>
       <c r="B4">
-        <v>0.39380616513717631</v>
-      </c>
-      <c r="C4" s="11">
+        <v>2.3532788682682399E-2</v>
+      </c>
+      <c r="C4" s="10">
         <v>89.47</v>
       </c>
       <c r="D4" s="11">
         <v>99.594893199116129</v>
       </c>
       <c r="E4" s="11">
-        <v>0.49137238320095472</v>
+        <f t="shared" ref="E4:E33" si="0">B4*1000000/C4/1000</f>
+        <v>0.26302435098560856</v>
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="11" t="s">
-        <v>11</v>
+      <c r="A5" s="32" t="s">
+        <v>10</v>
       </c>
       <c r="B5">
-        <v>2.0117011434536329</v>
-      </c>
-      <c r="C5" s="11">
+        <v>9.5742337555794504E-2</v>
+      </c>
+      <c r="C5" s="10">
         <v>2025.93</v>
       </c>
       <c r="D5" s="11">
         <v>41.559481240326626</v>
       </c>
       <c r="E5" s="11">
-        <v>9.9181313892104855E-2</v>
+        <f t="shared" si="0"/>
+        <v>4.7258462807596761E-2</v>
       </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="11" t="s">
-        <v>13</v>
+      <c r="A6" s="32" t="s">
+        <v>12</v>
       </c>
       <c r="B6">
-        <v>1.264887599939152</v>
-      </c>
-      <c r="C6" s="11">
+        <v>1.45218481483351E-2</v>
+      </c>
+      <c r="C6" s="10">
         <v>841.1</v>
       </c>
       <c r="D6" s="11">
         <v>5.6727238489784382</v>
       </c>
       <c r="E6" s="11">
-        <v>0.16129658957838663</v>
+        <f t="shared" si="0"/>
+        <v>1.7265305134151823E-2</v>
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="11" t="s">
-        <v>15</v>
+      <c r="A7" s="32" t="s">
+        <v>16</v>
       </c>
       <c r="B7">
-        <v>6.9574579554963529</v>
-      </c>
-      <c r="C7" s="11">
+        <v>5.9646896221161101E-2</v>
+      </c>
+      <c r="C7" s="10">
         <v>2710.93</v>
       </c>
       <c r="D7" s="11">
         <v>99.87565228251367</v>
       </c>
       <c r="E7" s="11">
-        <v>0.25588912628826216</v>
+        <f t="shared" si="0"/>
+        <v>2.2002374174604693E-2</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="11" t="s">
-        <v>17</v>
+      <c r="A8" s="32" t="s">
+        <v>14</v>
       </c>
       <c r="B8">
-        <v>4.0343838435018213</v>
-      </c>
-      <c r="C8" s="11">
+        <v>0.33651009445411101</v>
+      </c>
+      <c r="C8" s="10">
         <v>2229.5100000000002</v>
       </c>
       <c r="D8" s="11">
         <v>6.8638842174998729</v>
       </c>
       <c r="E8" s="11">
-        <v>0.18009304298854217</v>
+        <f t="shared" si="0"/>
+        <v>0.15093455263897043</v>
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="11" t="s">
-        <v>19</v>
+      <c r="A9" s="32" t="s">
+        <v>18</v>
       </c>
       <c r="B9">
-        <v>5.8171364869304663</v>
-      </c>
-      <c r="C9" s="11">
+        <v>7.8197999685334599E-2</v>
+      </c>
+      <c r="C9" s="10">
         <v>2834.72</v>
       </c>
       <c r="D9" s="11">
         <v>26.076880447377697</v>
       </c>
       <c r="E9" s="11">
-        <v>0.19901229601386497</v>
+        <f t="shared" si="0"/>
+        <v>2.7585793194860375E-2</v>
       </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="11" t="s">
-        <v>21</v>
+      <c r="A10" s="32" t="s">
+        <v>20</v>
       </c>
       <c r="B10">
-        <v>2.9348574887960144</v>
-      </c>
-      <c r="C10" s="11">
+        <v>5.2377982894905403E-2</v>
+      </c>
+      <c r="C10" s="10">
         <v>2773.8</v>
       </c>
       <c r="D10" s="11">
         <v>58.164277276240753</v>
       </c>
       <c r="E10" s="11">
-        <v>0.1017458101332334</v>
+        <f t="shared" si="0"/>
+        <v>1.8883114462075638E-2</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="11" t="s">
-        <v>23</v>
+      <c r="A11" s="32" t="s">
+        <v>22</v>
       </c>
       <c r="B11">
-        <v>0.74625796498034003</v>
-      </c>
-      <c r="C11" s="11">
+        <v>1.0559345649209099E-2</v>
+      </c>
+      <c r="C11" s="10">
         <v>273.58999999999997</v>
       </c>
       <c r="D11" s="11">
         <v>0</v>
       </c>
       <c r="E11" s="11">
-        <v>0.26779153259483585</v>
+        <f t="shared" si="0"/>
+        <v>3.859551024967689E-2</v>
       </c>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="11" t="s">
-        <v>25</v>
+      <c r="A12" s="32" t="s">
+        <v>24</v>
       </c>
       <c r="B12">
-        <v>27.671992282047007</v>
-      </c>
-      <c r="C12" s="11">
+        <v>1.26642158308516</v>
+      </c>
+      <c r="C12" s="10">
         <v>6455.19</v>
       </c>
       <c r="D12" s="11">
         <v>98.724884616719294</v>
       </c>
       <c r="E12" s="11">
-        <v>0.43768419023491784</v>
+        <f t="shared" si="0"/>
+        <v>0.19618656973461046</v>
       </c>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="11" t="s">
-        <v>27</v>
+      <c r="A13" s="32" t="s">
+        <v>28</v>
       </c>
       <c r="B13">
-        <v>21.202822939152369</v>
-      </c>
-      <c r="C13" s="11">
+        <v>2.1530778530804402</v>
+      </c>
+      <c r="C13" s="10">
         <v>14743.09</v>
       </c>
       <c r="D13" s="11">
         <v>66.440509510716112</v>
       </c>
       <c r="E13" s="11">
-        <v>0.14248366680772404</v>
+        <f t="shared" si="0"/>
+        <v>0.1460397958013171</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="11" t="s">
-        <v>29</v>
+      <c r="A14" s="32" t="s">
+        <v>26</v>
       </c>
       <c r="B14">
-        <v>39.590156827992317</v>
-      </c>
-      <c r="C14" s="11">
+        <v>0.90660082360618799</v>
+      </c>
+      <c r="C14" s="10">
         <v>10785.29</v>
       </c>
       <c r="D14" s="11">
         <v>94.174746750627875</v>
       </c>
       <c r="E14" s="11">
-        <v>0.36839915019284997</v>
+        <f t="shared" si="0"/>
+        <v>8.405901219217915E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="11" t="s">
-        <v>31</v>
+      <c r="A15" s="31" t="s">
+        <v>30</v>
       </c>
       <c r="B15">
-        <v>11.688841507043589</v>
-      </c>
-      <c r="C15" s="11">
+        <v>0.19785647319402</v>
+      </c>
+      <c r="C15" s="10">
         <v>4706.97</v>
       </c>
       <c r="D15" s="11">
         <v>44.231396446656937</v>
       </c>
       <c r="E15" s="11">
-        <v>0.24932420153463056</v>
+        <f t="shared" si="0"/>
+        <v>4.203478526398511E-2</v>
       </c>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="11" t="s">
-        <v>33</v>
+      <c r="A16" s="32" t="s">
+        <v>32</v>
       </c>
       <c r="B16">
-        <v>8.0166468035900103</v>
-      </c>
-      <c r="C16" s="11">
+        <v>0.13102481382636699</v>
+      </c>
+      <c r="C16" s="10">
         <v>4763.4799999999996</v>
       </c>
       <c r="D16" s="11">
         <v>9.8175096591700992</v>
       </c>
       <c r="E16" s="11">
-        <v>0.16251013545035903</v>
+        <f t="shared" si="0"/>
+        <v>2.7506111881726598E-2</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="11" t="s">
-        <v>35</v>
+      <c r="A17" s="32" t="s">
+        <v>40</v>
       </c>
       <c r="B17">
-        <v>13.94407940371201</v>
-      </c>
-      <c r="C17" s="11">
+        <v>0.45577613407732498</v>
+      </c>
+      <c r="C17" s="10">
         <v>6984.73</v>
       </c>
       <c r="D17" s="11">
         <v>97.838490831037788</v>
       </c>
       <c r="E17" s="11">
-        <v>0.20031680153638282</v>
+        <f t="shared" si="0"/>
+        <v>6.5253221538602788E-2</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="11" t="s">
-        <v>37</v>
+      <c r="A18" s="32" t="s">
+        <v>36</v>
       </c>
       <c r="B18">
-        <v>10.166223663011781</v>
-      </c>
-      <c r="C18" s="11">
+        <v>0.30814222342198599</v>
+      </c>
+      <c r="C18" s="10">
         <v>5458.94</v>
       </c>
       <c r="D18" s="11">
         <v>56.440766055090855</v>
       </c>
       <c r="E18" s="11">
-        <v>0.18121606665920603</v>
+        <f t="shared" si="0"/>
+        <v>5.644726328224637E-2</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="11" t="s">
-        <v>39</v>
+      <c r="A19" s="32" t="s">
+        <v>38</v>
       </c>
       <c r="B19">
-        <v>5.7323876271565295</v>
-      </c>
-      <c r="C19" s="11">
+        <v>6.66117138401775E-2</v>
+      </c>
+      <c r="C19" s="10">
         <v>3774.29</v>
       </c>
       <c r="D19" s="11">
         <v>2.0791554895781785</v>
       </c>
       <c r="E19" s="11">
-        <v>0.15077723225255107</v>
+        <f t="shared" si="0"/>
+        <v>1.7648806488154724E-2</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="11" t="s">
-        <v>41</v>
+      <c r="A20" s="32" t="s">
+        <v>42</v>
       </c>
       <c r="B20">
-        <v>12.017816770779381</v>
-      </c>
-      <c r="C20" s="11">
+        <v>0.417375135737027</v>
+      </c>
+      <c r="C20" s="10">
         <v>5825.61</v>
       </c>
       <c r="D20" s="11">
         <v>84.589009893810285</v>
       </c>
       <c r="E20" s="11">
-        <v>0.21133795487302856</v>
+        <f t="shared" si="0"/>
+        <v>7.1644881091770127E-2</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="11" t="s">
-        <v>43</v>
+      <c r="A21" s="32" t="s">
+        <v>34</v>
       </c>
       <c r="B21">
-        <v>6.2748058451248196</v>
-      </c>
-      <c r="C21" s="11">
+        <v>0.32615864981383202</v>
+      </c>
+      <c r="C21" s="10">
         <v>3578.39</v>
       </c>
       <c r="D21" s="11">
         <v>84.863671420146076</v>
       </c>
       <c r="E21" s="11">
-        <v>0.17700428379230254</v>
+        <f t="shared" si="0"/>
+        <v>9.114675868584253E-2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="11" t="s">
-        <v>45</v>
+      <c r="A22" s="32" t="s">
+        <v>44</v>
       </c>
       <c r="B22">
-        <v>1.585662081469676</v>
-      </c>
-      <c r="C22" s="11">
+        <v>6.3708399270193797E-2</v>
+      </c>
+      <c r="C22" s="10">
         <v>693.89</v>
       </c>
       <c r="D22" s="11">
         <v>95.801510788364425</v>
       </c>
       <c r="E22" s="11">
-        <v>0.25203351808607399</v>
+        <f t="shared" si="0"/>
+        <v>9.1813398766654369E-2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="11" t="s">
-        <v>47</v>
+      <c r="A23" s="32" t="s">
+        <v>46</v>
       </c>
       <c r="B23">
-        <v>1.2655675188222211</v>
-      </c>
-      <c r="C23" s="11">
+        <v>2.39216791086409E-2</v>
+      </c>
+      <c r="C23" s="10">
         <v>304.89999999999998</v>
       </c>
       <c r="D23" s="11">
         <v>100</v>
       </c>
       <c r="E23" s="11">
-        <v>0.45692855095511897</v>
+        <f t="shared" si="0"/>
+        <v>7.8457458539327313E-2</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="11" t="s">
-        <v>49</v>
+      <c r="A24" s="32" t="s">
+        <v>56</v>
       </c>
       <c r="B24">
-        <v>5.1589930043054251</v>
-      </c>
-      <c r="C24" s="11">
+        <v>0.32200548493151698</v>
+      </c>
+      <c r="C24" s="10">
         <v>3022.97</v>
       </c>
       <c r="D24" s="11">
         <v>95.332076039702144</v>
       </c>
       <c r="E24" s="11">
-        <v>0.16689984887869211</v>
+        <f t="shared" si="0"/>
+        <v>0.10651957675118079</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="11" t="s">
-        <v>51</v>
+      <c r="A25" s="32" t="s">
+        <v>50</v>
       </c>
       <c r="B25">
-        <v>32.428693590839657</v>
-      </c>
-      <c r="C25" s="11">
+        <v>1.9463631631415499</v>
+      </c>
+      <c r="C25" s="10">
         <v>8387.9</v>
       </c>
       <c r="D25" s="11">
         <v>98.735941874099751</v>
       </c>
       <c r="E25" s="11">
-        <v>0.38665965457800233</v>
+        <f t="shared" si="0"/>
+        <v>0.23204415445362367</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="11" t="s">
-        <v>53</v>
+      <c r="A26" s="32" t="s">
+        <v>52</v>
       </c>
       <c r="B26">
-        <v>0.2902811825768854</v>
-      </c>
-      <c r="C26" s="11">
+        <v>7.1533763491744597E-3</v>
+      </c>
+      <c r="C26" s="10">
         <v>127.17</v>
       </c>
       <c r="D26" s="11">
         <v>15.683581124757598</v>
       </c>
       <c r="E26" s="11">
-        <v>0.23161435101579622</v>
+        <f t="shared" si="0"/>
+        <v>5.6250502077333175E-2</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="11" t="s">
-        <v>55</v>
+      <c r="A27" s="32" t="s">
+        <v>48</v>
       </c>
       <c r="B27">
-        <v>4.7928681636867161</v>
-      </c>
-      <c r="C27" s="11">
+        <v>0.273519868239542</v>
+      </c>
+      <c r="C27" s="10">
         <v>3160.96</v>
       </c>
       <c r="D27" s="11">
         <v>99.90715417029017</v>
       </c>
       <c r="E27" s="11">
-        <v>0.15500535779792407</v>
+        <f t="shared" si="0"/>
+        <v>8.6530632541867658E-2</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="11" t="s">
-        <v>57</v>
+      <c r="A28" s="32" t="s">
+        <v>54</v>
       </c>
       <c r="B28">
-        <v>7.4305441339184597</v>
-      </c>
-      <c r="C28" s="11">
+        <v>0.41347254480915901</v>
+      </c>
+      <c r="C28" s="10">
         <v>6403.97</v>
       </c>
       <c r="D28" s="11">
         <v>57.130244877096793</v>
       </c>
       <c r="E28" s="11">
-        <v>0.11612568523321799</v>
+        <f t="shared" si="0"/>
+        <v>6.4565034628388182E-2</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="11" t="s">
-        <v>59</v>
+      <c r="A29" s="31" t="s">
+        <v>58</v>
       </c>
       <c r="B29">
-        <v>0.61143497499256494</v>
-      </c>
-      <c r="C29" s="11">
+        <v>7.5404454839990698E-2</v>
+      </c>
+      <c r="C29" s="10">
         <v>390.03</v>
       </c>
       <c r="D29" s="11">
         <v>85.469394355947287</v>
       </c>
       <c r="E29" s="11">
-        <v>0.15010849787281699</v>
+        <f t="shared" si="0"/>
+        <v>0.1933298844704015</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="11" t="s">
-        <v>61</v>
+      <c r="A30" s="32" t="s">
+        <v>62</v>
       </c>
       <c r="B30">
-        <v>2.6584786778179761</v>
-      </c>
-      <c r="C30" s="11">
-        <v>194.58</v>
+        <v>0.14881950441484401</v>
+      </c>
+      <c r="C30" s="10">
+        <v>2824.76</v>
       </c>
       <c r="D30" s="11">
         <v>97.779499096307774</v>
       </c>
       <c r="E30" s="11">
-        <v>1.0515036231933832</v>
+        <f t="shared" si="0"/>
+        <v>5.2683946393620694E-2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="11" t="s">
-        <v>63</v>
+      <c r="A31" s="32" t="s">
+        <v>60</v>
       </c>
       <c r="B31">
-        <v>10.242653307524719</v>
-      </c>
-      <c r="C31" s="11">
-        <v>2824.76</v>
+        <v>3.0312087731685401E-3</v>
+      </c>
+      <c r="C31" s="12">
+        <v>194.58</v>
       </c>
       <c r="D31" s="11">
         <v>98.524118472527761</v>
       </c>
       <c r="E31" s="11">
-        <v>0.35946741750772426</v>
+        <f t="shared" si="0"/>
+        <v>1.5578213450347107E-2</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="11" t="s">
-        <v>65</v>
+      <c r="A32" s="32" t="s">
+        <v>64</v>
       </c>
       <c r="B32">
-        <v>4.3079580487557356</v>
-      </c>
-      <c r="C32" s="11">
+        <v>6.0134137175909E-2</v>
+      </c>
+      <c r="C32" s="10">
         <v>4243.22</v>
       </c>
       <c r="D32" s="11">
         <v>76.298746324957008</v>
       </c>
       <c r="E32" s="11">
-        <v>0.10547678796352263</v>
+        <f t="shared" si="0"/>
+        <v>1.4171816963510966E-2</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="11" t="s">
-        <v>67</v>
+      <c r="A33" s="32" t="s">
+        <v>66</v>
       </c>
       <c r="B33">
-        <v>1.5017382292890908</v>
-      </c>
-      <c r="C33" s="11">
+        <v>6.6662327397583598E-2</v>
+      </c>
+      <c r="C33" s="10">
         <v>1024.68</v>
       </c>
       <c r="D33" s="11">
         <v>21.770995310936726</v>
       </c>
       <c r="E33" s="11">
-        <v>0.14965890667208914</v>
+        <f t="shared" si="0"/>
+        <v>6.5056727366186118E-2</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:E33">
+    <sortCondition ref="A3:A33"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4183,379 +4964,1420 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B85D2353-F5BD-C745-AFFD-F3A994FB67F7}">
-  <dimension ref="A1:C33"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="13"/>
+    <col min="1" max="1" width="10.83203125" style="16"/>
     <col min="2" max="3" width="10.83203125" style="12"/>
-    <col min="4" max="4" width="14.1640625" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="10.83203125" style="11"/>
+    <col min="4" max="4" width="10.83203125" style="15"/>
+    <col min="5" max="5" width="28.5" style="16" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="15"/>
+    <col min="7" max="7" width="19.1640625" style="15" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.1640625" style="15" customWidth="1"/>
+    <col min="9" max="9" width="26" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="10.83203125" style="11"/>
+    <col min="15" max="15" width="14.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="10.83203125" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:15">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="J1" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" s="14" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
-        <v>69</v>
+      <c r="G2" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="J2" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="18"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" s="16" t="s">
+        <v>68</v>
       </c>
       <c r="B3" s="12">
-        <v>-13.552328450957299</v>
+        <v>-10.908241681538982</v>
       </c>
       <c r="C3" s="12">
         <v>17.224346627655425</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="13" t="s">
-        <v>70</v>
+      <c r="D3" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="19">
+        <v>58.942717461710295</v>
+      </c>
+      <c r="F3" s="14">
+        <v>7334.46</v>
+      </c>
+      <c r="G3" s="14">
+        <v>4150.75</v>
+      </c>
+      <c r="H3" s="19">
+        <v>67.589689804199438</v>
+      </c>
+      <c r="I3" s="14">
+        <v>7044.56</v>
+      </c>
+      <c r="J3" s="12">
+        <v>3540.86</v>
+      </c>
+      <c r="L3" s="18"/>
+      <c r="M3" s="36" t="s">
+        <v>7</v>
+      </c>
+      <c r="N3">
+        <v>-6.6657354103160458</v>
+      </c>
+      <c r="O3">
+        <v>-10.908241681538982</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="16" t="s">
+        <v>69</v>
       </c>
       <c r="B4" s="12">
-        <v>-48.009996979606832</v>
+        <v>-39.054435983205316</v>
       </c>
       <c r="C4" s="12">
         <v>-50.296473525434301</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="13" t="s">
-        <v>71</v>
+      <c r="D4" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="19">
+        <v>0.72296990075272094</v>
+      </c>
+      <c r="F4" s="14">
+        <v>89.47</v>
+      </c>
+      <c r="G4" s="14">
+        <v>47.78</v>
+      </c>
+      <c r="H4" s="19">
+        <v>1.322169033698475</v>
+      </c>
+      <c r="I4" s="14">
+        <v>158.91</v>
+      </c>
+      <c r="J4" s="12">
+        <v>96.13</v>
+      </c>
+      <c r="L4" s="18"/>
+      <c r="M4" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="N4">
+        <v>-0.3788208402298322</v>
+      </c>
+      <c r="O4">
+        <v>-39.054435983205316</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="16" t="s">
+        <v>70</v>
       </c>
       <c r="B5" s="12">
-        <v>-26.996621271389444</v>
+        <v>-24.199228873172139</v>
       </c>
       <c r="C5" s="12">
         <v>3.8620101407382834</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="13" t="s">
-        <v>74</v>
+      <c r="D5" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="19">
+        <v>10.723820296945991</v>
+      </c>
+      <c r="F5" s="14">
+        <v>2025.93</v>
+      </c>
+      <c r="G5" s="14">
+        <v>1095.9000000000001</v>
+      </c>
+      <c r="H5" s="19">
+        <v>14.166237359079625</v>
+      </c>
+      <c r="I5" s="14">
+        <v>2059.4499999999998</v>
+      </c>
+      <c r="J5" s="12">
+        <v>1055.1500000000001</v>
+      </c>
+      <c r="L5" s="18"/>
+      <c r="M5" s="36" t="s">
+        <v>10</v>
+      </c>
+      <c r="N5">
+        <v>-2.9392541058344026</v>
+      </c>
+      <c r="O5">
+        <v>-24.199228873172139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="16" t="s">
+        <v>73</v>
       </c>
       <c r="B6" s="12">
-        <v>-51.807065661138694</v>
+        <v>-53.697913572211128</v>
       </c>
       <c r="C6" s="12">
         <v>-4.4344280691254445</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="13" t="s">
-        <v>72</v>
+      <c r="D6" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="19">
+        <v>7.6487337451780926</v>
+      </c>
+      <c r="F6" s="14">
+        <v>841.1</v>
+      </c>
+      <c r="G6" s="14">
+        <v>510.97</v>
+      </c>
+      <c r="H6" s="19">
+        <v>15.024158698883435</v>
+      </c>
+      <c r="I6" s="14">
+        <v>943.71</v>
+      </c>
+      <c r="J6" s="12">
+        <v>534.67999999999995</v>
+      </c>
+      <c r="L6" s="18"/>
+      <c r="M6" s="36" t="s">
+        <v>12</v>
+      </c>
+      <c r="N6">
+        <v>-6.9171734724118226</v>
+      </c>
+      <c r="O6">
+        <v>-53.697913572211128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="16" t="s">
+        <v>74</v>
       </c>
       <c r="B7" s="12">
-        <v>14.023153210134678</v>
+        <v>-32.765416216801171</v>
       </c>
       <c r="C7" s="12">
+        <v>6.8782848779189703</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="19">
+        <v>25.221590456396985</v>
+      </c>
+      <c r="F7" s="14">
+        <v>2229.5100000000002</v>
+      </c>
+      <c r="G7" s="14">
+        <v>1285.19</v>
+      </c>
+      <c r="H7" s="19">
+        <v>36.777165732048587</v>
+      </c>
+      <c r="I7" s="14">
+        <v>2266.52</v>
+      </c>
+      <c r="J7" s="12">
+        <v>1202.48</v>
+      </c>
+      <c r="L7" s="18"/>
+      <c r="M7" s="36" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7">
+        <v>-10.604568566069357</v>
+      </c>
+      <c r="O7">
+        <v>-32.765416216801171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="12">
+        <v>24.493908606401803</v>
+      </c>
+      <c r="C8" s="12">
         <v>13.909098230824993</v>
       </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="13" t="s">
+      <c r="D8" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="19">
+        <v>10.127456556009038</v>
+      </c>
+      <c r="F8" s="14">
+        <v>2710.93</v>
+      </c>
+      <c r="G8" s="14">
+        <v>1272.9000000000001</v>
+      </c>
+      <c r="H8" s="19">
+        <v>8.7901664995419626</v>
+      </c>
+      <c r="I8" s="14">
+        <v>2750.87</v>
+      </c>
+      <c r="J8" s="12">
+        <v>1117.47</v>
+      </c>
+      <c r="L8" s="18"/>
+      <c r="M8" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="N8">
+        <v>1.7355088223900266</v>
+      </c>
+      <c r="O8">
+        <v>24.493908606401803</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="12">
-        <v>-32.692847978141245</v>
-      </c>
-      <c r="C8" s="12">
-        <v>6.8782848779189703</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="13" t="s">
-        <v>76</v>
-      </c>
       <c r="B9" s="12">
-        <v>-33.754661353328643</v>
+        <v>-33.508814584473754</v>
       </c>
       <c r="C9" s="12">
         <v>-3.8153731621068396</v>
       </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="13" t="s">
-        <v>77</v>
+      <c r="D9" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="19">
+        <v>25.123575264253095</v>
+      </c>
+      <c r="F9" s="14">
+        <v>2834.72</v>
+      </c>
+      <c r="G9" s="14">
+        <v>1395.36</v>
+      </c>
+      <c r="H9" s="19">
+        <v>36.465396659791907</v>
+      </c>
+      <c r="I9" s="14">
+        <v>2974.13</v>
+      </c>
+      <c r="J9" s="12">
+        <v>1450.71</v>
+      </c>
+      <c r="L9" s="18"/>
+      <c r="M9" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="N9">
+        <v>-11.069440505196695</v>
+      </c>
+      <c r="O9">
+        <v>-33.508814584473754</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="16" t="s">
+        <v>76</v>
       </c>
       <c r="B10" s="12">
-        <v>-24.338366669958759</v>
+        <v>-22.059299812443346</v>
       </c>
       <c r="C10" s="12">
         <v>4.0836625610039565</v>
       </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="13" t="s">
-        <v>78</v>
+      <c r="D10" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="19">
+        <v>10.211564386096354</v>
+      </c>
+      <c r="F10" s="14">
+        <v>2773.8</v>
+      </c>
+      <c r="G10" s="14">
+        <v>1119.68</v>
+      </c>
+      <c r="H10" s="19">
+        <v>12.941308712276129</v>
+      </c>
+      <c r="I10" s="14">
+        <v>3090.86</v>
+      </c>
+      <c r="J10" s="12">
+        <v>1075.75</v>
+      </c>
+      <c r="L10" s="18"/>
+      <c r="M10" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="N10">
+        <v>-2.4495776810841559</v>
+      </c>
+      <c r="O10">
+        <v>-22.059299812443346</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="16" t="s">
+        <v>77</v>
       </c>
       <c r="B11" s="12">
-        <v>-42.814133603304789</v>
+        <v>-45.013229554106914</v>
       </c>
       <c r="C11" s="12">
         <v>-12.773657668347671</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="13" t="s">
-        <v>79</v>
+      <c r="D11" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="19">
+        <v>3.6373529412489014</v>
+      </c>
+      <c r="F11" s="14">
+        <v>273.58999999999997</v>
+      </c>
+      <c r="G11" s="14">
+        <v>147.02000000000001</v>
+      </c>
+      <c r="H11" s="19">
+        <v>6.1539249676148096</v>
+      </c>
+      <c r="I11" s="14">
+        <v>365.47</v>
+      </c>
+      <c r="J11" s="12">
+        <v>168.55</v>
+      </c>
+      <c r="L11" s="18"/>
+      <c r="M11" s="36" t="s">
+        <v>22</v>
+      </c>
+      <c r="N11">
+        <v>-2.4177086210792695</v>
+      </c>
+      <c r="O11">
+        <v>-45.013229554106914</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="16" t="s">
+        <v>78</v>
       </c>
       <c r="B12" s="12">
-        <v>-15.479326106626401</v>
+        <v>-9.866823968841091</v>
       </c>
       <c r="C12" s="12">
         <v>6.2777729736364263</v>
       </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="13" t="s">
+      <c r="D12" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="19">
+        <v>39.568015713843018</v>
+      </c>
+      <c r="F12" s="14">
+        <v>6455.19</v>
+      </c>
+      <c r="G12" s="14">
+        <v>3809.92</v>
+      </c>
+      <c r="H12" s="19">
+        <v>45.027186769139277</v>
+      </c>
+      <c r="I12" s="14">
+        <v>6607.32</v>
+      </c>
+      <c r="J12" s="13">
+        <v>3584.87</v>
+      </c>
+      <c r="L12" s="18"/>
+      <c r="M12" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="N12">
+        <v>-3.8506866074827357</v>
+      </c>
+      <c r="O12">
+        <v>-9.866823968841091</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="16" t="s">
         <v>80</v>
       </c>
       <c r="B13" s="12">
-        <v>7.482185906298783</v>
+        <v>-10.273768520162353</v>
       </c>
       <c r="C13" s="12">
+        <v>9.9682924399880513</v>
+      </c>
+      <c r="D13" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="19">
+        <v>70.717559493479058</v>
+      </c>
+      <c r="F13" s="14">
+        <v>10785.29</v>
+      </c>
+      <c r="G13" s="14">
+        <v>6624.27</v>
+      </c>
+      <c r="H13" s="19">
+        <v>80.226043691123976</v>
+      </c>
+      <c r="I13" s="15">
+        <v>10697.43</v>
+      </c>
+      <c r="J13" s="12">
+        <v>6023.8</v>
+      </c>
+      <c r="L13" s="18"/>
+      <c r="M13" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="N13">
+        <v>-6.9628611293370355</v>
+      </c>
+      <c r="O13">
+        <v>-10.273768520162353</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="12">
+        <v>7.0020943283850281</v>
+      </c>
+      <c r="C14" s="12">
         <v>10.391191632731461</v>
       </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" s="13" t="s">
+      <c r="D14" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="19">
+        <v>94.394767008528305</v>
+      </c>
+      <c r="F14" s="14">
+        <v>14743.09</v>
+      </c>
+      <c r="G14" s="14">
+        <v>7788.22</v>
+      </c>
+      <c r="H14" s="19">
+        <v>88.598402348027378</v>
+      </c>
+      <c r="I14" s="14">
+        <v>13575.56</v>
+      </c>
+      <c r="J14" s="12">
+        <v>7055.11</v>
+      </c>
+      <c r="L14" s="18"/>
+      <c r="M14" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14">
+        <v>5.959011802388261</v>
+      </c>
+      <c r="O14">
+        <v>7.0020943283850281</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="B14" s="12">
-        <v>-14.862464573612574</v>
-      </c>
-      <c r="C14" s="12">
-        <v>9.9682924399880513</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" s="13" t="s">
-        <v>82</v>
-      </c>
       <c r="B15" s="12">
-        <v>-17.180589001146796</v>
+        <v>-13.269693508731194</v>
       </c>
       <c r="C15" s="12">
         <v>7.3787511454986232</v>
       </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" s="13" t="s">
-        <v>83</v>
+      <c r="D15" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="19">
+        <v>46.163253907706853</v>
+      </c>
+      <c r="F15" s="14">
+        <v>4706.97</v>
+      </c>
+      <c r="G15" s="14">
+        <v>2777.04</v>
+      </c>
+      <c r="H15" s="19">
+        <v>54.841944976184379</v>
+      </c>
+      <c r="I15" s="14">
+        <v>4416.6000000000004</v>
+      </c>
+      <c r="J15" s="12">
+        <v>2586.21</v>
+      </c>
+      <c r="L15" s="18"/>
+      <c r="M15" s="36" t="s">
+        <v>30</v>
+      </c>
+      <c r="N15">
+        <v>-6.353976348089013</v>
+      </c>
+      <c r="O15">
+        <v>-13.269693508731194</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="16" t="s">
+        <v>82</v>
       </c>
       <c r="B16" s="12">
-        <v>-40.42416183496568</v>
+        <v>-39.969343126548587</v>
       </c>
       <c r="C16" s="12">
         <v>2.6248185339550654</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" s="13" t="s">
+      <c r="D16" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="19">
+        <v>44.958510439192324</v>
+      </c>
+      <c r="F16" s="14">
+        <v>4763.4799999999996</v>
+      </c>
+      <c r="G16" s="14">
+        <v>3068.01</v>
+      </c>
+      <c r="H16" s="19">
+        <v>73.419802218351592</v>
+      </c>
+      <c r="I16" s="14">
+        <v>5009.99</v>
+      </c>
+      <c r="J16" s="12">
+        <v>2989.54</v>
+      </c>
+      <c r="L16" s="18"/>
+      <c r="M16" s="36" t="s">
+        <v>32</v>
+      </c>
+      <c r="N16">
+        <v>-27.45502180883777</v>
+      </c>
+      <c r="O16">
+        <v>-39.969343126548587</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="12">
+        <v>8.6564142307003227</v>
+      </c>
+      <c r="C17" s="12">
+        <v>11.245449472537397</v>
+      </c>
+      <c r="D17" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="19">
+        <v>34.218511569548681</v>
+      </c>
+      <c r="F17" s="14">
+        <v>5825.61</v>
+      </c>
+      <c r="G17" s="14">
+        <v>4186.5</v>
+      </c>
+      <c r="H17" s="19">
+        <v>32.051579718799999</v>
+      </c>
+      <c r="I17" s="14">
+        <v>5132.05</v>
+      </c>
+      <c r="J17" s="12">
+        <v>3763.3</v>
+      </c>
+      <c r="L17" s="18"/>
+      <c r="M17" s="36" t="s">
+        <v>40</v>
+      </c>
+      <c r="N17">
+        <v>2.4550472005586066</v>
+      </c>
+      <c r="O17">
+        <v>8.6564142307003227</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="B17" s="12">
-        <v>3.8169340713046673</v>
-      </c>
-      <c r="C17" s="12">
-        <v>28.899716005315135</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="13" t="s">
-        <v>85</v>
-      </c>
       <c r="B18" s="12">
-        <v>-21.886507966311594</v>
+        <v>-19.987346437828911</v>
       </c>
       <c r="C18" s="12">
         <v>10.37194622212146</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" s="13" t="s">
-        <v>86</v>
+      <c r="D18" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="19">
+        <v>50.054313882637047</v>
+      </c>
+      <c r="F18" s="14">
+        <v>5458.94</v>
+      </c>
+      <c r="G18" s="14">
+        <v>3797.7</v>
+      </c>
+      <c r="H18" s="19">
+        <v>63.465668463645422</v>
+      </c>
+      <c r="I18" s="14">
+        <v>5475.22</v>
+      </c>
+      <c r="J18" s="13">
+        <v>3440.82</v>
+      </c>
+      <c r="L18" s="18"/>
+      <c r="M18" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="N18">
+        <v>-11.185317912447275</v>
+      </c>
+      <c r="O18">
+        <v>-19.987346437828911</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="16" t="s">
+        <v>85</v>
       </c>
       <c r="B19" s="12">
-        <v>-34.17183554247616</v>
+        <v>-33.754386138783346</v>
       </c>
       <c r="C19" s="12">
         <v>0.73039860335323781</v>
       </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" s="13" t="s">
+      <c r="D19" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="19">
+        <v>37.911175699307741</v>
+      </c>
+      <c r="F19" s="14">
+        <v>3774.29</v>
+      </c>
+      <c r="G19" s="14">
+        <v>2198.31</v>
+      </c>
+      <c r="H19" s="19">
+        <v>57.030148987724132</v>
+      </c>
+      <c r="I19" s="14">
+        <v>3775.26</v>
+      </c>
+      <c r="J19" s="12">
+        <v>2182.37</v>
+      </c>
+      <c r="L19" s="18"/>
+      <c r="M19" s="36" t="s">
+        <v>38</v>
+      </c>
+      <c r="N19">
+        <v>-18.505409946318572</v>
+      </c>
+      <c r="O19">
+        <v>-33.754386138783346</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="16" t="s">
         <v>87</v>
       </c>
       <c r="B20" s="12">
-        <v>6.5085396367223698</v>
+        <v>-11.160110248842416</v>
       </c>
       <c r="C20" s="12">
-        <v>11.245449472537397</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" s="13" t="s">
+        <v>8.9274256260331253</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="19">
+        <v>20.796616893488086</v>
+      </c>
+      <c r="F20" s="14">
+        <v>3578.39</v>
+      </c>
+      <c r="G20" s="14">
+        <v>2563.4</v>
+      </c>
+      <c r="H20" s="19">
+        <v>23.792580607606514</v>
+      </c>
+      <c r="I20" s="14">
+        <v>3412.42</v>
+      </c>
+      <c r="J20" s="12">
+        <v>2353.31</v>
+      </c>
+      <c r="L20" s="18"/>
+      <c r="M20" s="36" t="s">
+        <v>42</v>
+      </c>
+      <c r="N20">
+        <v>-2.3100346378918992</v>
+      </c>
+      <c r="O20">
+        <v>-11.160110248842416</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="12">
+        <v>5.0508988393068286</v>
+      </c>
+      <c r="C21" s="12">
+        <v>28.899716005315135</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="19">
+        <v>23.558404117466363</v>
+      </c>
+      <c r="F21" s="14">
+        <v>6984.73</v>
+      </c>
+      <c r="G21" s="14">
+        <v>3957.84</v>
+      </c>
+      <c r="H21" s="19">
+        <v>22.700133116628844</v>
+      </c>
+      <c r="I21" s="14">
+        <v>6253.09</v>
+      </c>
+      <c r="J21" s="12">
+        <v>3070.48</v>
+      </c>
+      <c r="L21" s="18"/>
+      <c r="M21" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="N21">
+        <v>0.96483248553749945</v>
+      </c>
+      <c r="O21">
+        <v>5.0508988393068286</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="12">
-        <v>-16.130478622372099</v>
-      </c>
-      <c r="C21" s="12">
-        <v>8.9274256260331253</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" s="13" t="s">
-        <v>89</v>
-      </c>
       <c r="B22" s="12">
-        <v>-11.311345094000066</v>
+        <v>-6.4731578826205478</v>
       </c>
       <c r="C22" s="12">
         <v>1.4760641860215893</v>
       </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="13" t="s">
-        <v>90</v>
+      <c r="D22" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="19">
+        <v>3.7048392097787901</v>
+      </c>
+      <c r="F22" s="14">
+        <v>693.89</v>
+      </c>
+      <c r="G22" s="14">
+        <v>378.8</v>
+      </c>
+      <c r="H22" s="19">
+        <v>4.0777579463742786</v>
+      </c>
+      <c r="I22" s="14">
+        <v>755.79</v>
+      </c>
+      <c r="J22" s="13">
+        <v>373.29</v>
+      </c>
+      <c r="L22" s="18"/>
+      <c r="M22" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="N22">
+        <v>-0.21038487471492306</v>
+      </c>
+      <c r="O22">
+        <v>-6.4731578826205478</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="16" t="s">
+        <v>89</v>
       </c>
       <c r="B23" s="12">
-        <v>-4.4585510012684244</v>
+        <v>-1.1867511328897018</v>
       </c>
       <c r="C23" s="12">
         <v>12.24529212940609</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" s="13" t="s">
+      <c r="D23" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="19">
+        <v>1.5875475900252078</v>
+      </c>
+      <c r="F23" s="14">
+        <v>304.89999999999998</v>
+      </c>
+      <c r="G23" s="14">
+        <v>116.23</v>
+      </c>
+      <c r="H23" s="19">
+        <v>1.643633479723327</v>
+      </c>
+      <c r="I23" s="14">
+        <v>282.68</v>
+      </c>
+      <c r="J23" s="12">
+        <v>103.55</v>
+      </c>
+      <c r="L23" s="18"/>
+      <c r="M23" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="N23">
+        <v>-1.7357710833151963E-2</v>
+      </c>
+      <c r="O23">
+        <v>-1.1867511328897018</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="12">
+        <v>-21.418962654272537</v>
+      </c>
+      <c r="C24" s="12">
+        <v>7.7246812107695986</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="19">
+        <v>33.370951281191928</v>
+      </c>
+      <c r="F24" s="14">
+        <v>6403.97</v>
+      </c>
+      <c r="G24" s="14">
+        <v>3593.76</v>
+      </c>
+      <c r="H24" s="19">
+        <v>42.593194703396861</v>
+      </c>
+      <c r="I24" s="14">
+        <v>6269.93</v>
+      </c>
+      <c r="J24" s="12">
+        <v>3336.06</v>
+      </c>
+      <c r="L24" s="18"/>
+      <c r="M24" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="N24">
+        <v>-7.968815772440216</v>
+      </c>
+      <c r="O24">
+        <v>-21.418962654272537</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="16" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="12">
-        <v>-7.9165947335311975</v>
-      </c>
-      <c r="C24" s="12">
-        <v>9.3436867539548238</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" s="13" t="s">
-        <v>92</v>
-      </c>
       <c r="B25" s="12">
-        <v>-12.794744325511898</v>
+        <v>-5.9193554767627585</v>
       </c>
       <c r="C25" s="12">
         <v>15.805252035450422</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" s="13" t="s">
-        <v>93</v>
+      <c r="D25" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="19">
+        <v>49.924356130133489</v>
+      </c>
+      <c r="F25" s="14">
+        <v>8387.9</v>
+      </c>
+      <c r="G25" s="14">
+        <v>5655.28</v>
+      </c>
+      <c r="H25" s="19">
+        <v>54.996708211331125</v>
+      </c>
+      <c r="I25" s="15">
+        <v>8007.58</v>
+      </c>
+      <c r="J25" s="12">
+        <v>4883.4399999999996</v>
+      </c>
+      <c r="L25" s="18"/>
+      <c r="M25" s="36" t="s">
+        <v>50</v>
+      </c>
+      <c r="N25">
+        <v>-2.7898518582855374</v>
+      </c>
+      <c r="O25">
+        <v>-5.9193554767627585</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="16" t="s">
+        <v>92</v>
       </c>
       <c r="B26" s="12">
-        <v>-32.485945675399265</v>
+        <v>-30.539612080888904</v>
       </c>
       <c r="C26" s="12">
         <v>-20.823940924990289</v>
       </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" s="13" t="s">
-        <v>94</v>
+      <c r="D26" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="19">
+        <v>1.6271182138652531</v>
+      </c>
+      <c r="F26" s="14">
+        <v>127.17</v>
+      </c>
+      <c r="G26" s="14">
+        <v>101.86</v>
+      </c>
+      <c r="H26" s="19">
+        <v>2.3934615189759056</v>
+      </c>
+      <c r="I26" s="14">
+        <v>190.5</v>
+      </c>
+      <c r="J26" s="12">
+        <v>128.65</v>
+      </c>
+      <c r="L26" s="18"/>
+      <c r="M26" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="N26">
+        <v>-0.64916605696490759</v>
+      </c>
+      <c r="O26">
+        <v>-30.539612080888904</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="16" t="s">
+        <v>90</v>
       </c>
       <c r="B27" s="12">
-        <v>-10.076569629941964</v>
+        <v>-5.2464035044651594</v>
       </c>
       <c r="C27" s="12">
+        <v>9.3436867539548238</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E27" s="19">
+        <v>12.367138769613588</v>
+      </c>
+      <c r="F27" s="14">
+        <v>3022.97</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1323.66</v>
+      </c>
+      <c r="H27" s="19">
+        <v>13.098073555534492</v>
+      </c>
+      <c r="I27" s="14">
+        <v>3086.09</v>
+      </c>
+      <c r="J27" s="12">
+        <v>1210.55</v>
+      </c>
+      <c r="L27" s="18"/>
+      <c r="M27" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="N27">
+        <v>-0.49000208502024023</v>
+      </c>
+      <c r="O27">
+        <v>-5.2464035044651594</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="12">
+        <v>-0.67770060168819746</v>
+      </c>
+      <c r="C28" s="12">
         <v>8.5226980712329521</v>
       </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" s="13" t="s">
+      <c r="D28" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="19">
+        <v>8.5284683512363202</v>
+      </c>
+      <c r="F28" s="14">
+        <v>3160.96</v>
+      </c>
+      <c r="G28" s="14">
+        <v>1478.09</v>
+      </c>
+      <c r="H28" s="19">
+        <v>9.11514717438234</v>
+      </c>
+      <c r="I28" s="14">
+        <v>3245.2</v>
+      </c>
+      <c r="J28" s="12">
+        <v>1362.01</v>
+      </c>
+      <c r="L28" s="18"/>
+      <c r="M28" s="36" t="s">
+        <v>54</v>
+      </c>
+      <c r="N28">
+        <v>-4.8368218422907283E-2</v>
+      </c>
+      <c r="O28">
+        <v>-0.67770060168819746</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="12">
-        <v>-24.323943231925437</v>
-      </c>
-      <c r="C28" s="12">
-        <v>7.7246812107695986</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" s="13" t="s">
-        <v>96</v>
-      </c>
       <c r="B29" s="12">
-        <v>-46.942206963042295</v>
+        <v>-29.310824267814095</v>
       </c>
       <c r="C29" s="12">
         <v>44.121956717763751</v>
       </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" s="13" t="s">
+      <c r="D29" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="19">
+        <v>1.3807077502937468</v>
+      </c>
+      <c r="F29" s="14">
+        <v>390.03</v>
+      </c>
+      <c r="G29" s="14">
+        <v>255.73</v>
+      </c>
+      <c r="H29" s="19">
+        <v>2.1158812976732269</v>
+      </c>
+      <c r="I29" s="14">
+        <v>333.97</v>
+      </c>
+      <c r="J29" s="12">
+        <v>177.44</v>
+      </c>
+      <c r="L29" s="18"/>
+      <c r="M29" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="N29">
+        <v>-0.47905505293055084</v>
+      </c>
+      <c r="O29">
+        <v>-29.310824267814095</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="12">
+        <v>16.173490579800699</v>
+      </c>
+      <c r="C30" s="12">
+        <v>22.711138133703919</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="E30" s="19">
+        <v>16.357622467507575</v>
+      </c>
+      <c r="F30" s="14">
+        <v>2824.76</v>
+      </c>
+      <c r="G30" s="14">
+        <v>2119.16</v>
+      </c>
+      <c r="H30" s="19">
+        <v>13.736661279180067</v>
+      </c>
+      <c r="I30" s="14">
+        <v>2256.89</v>
+      </c>
+      <c r="J30" s="13">
+        <v>1726.95</v>
+      </c>
+      <c r="L30" s="18"/>
+      <c r="M30" s="35" t="s">
+        <v>125</v>
+      </c>
+      <c r="N30">
+        <v>-132.3215251120979</v>
+      </c>
+      <c r="O30">
+        <v>-16.173490579800728</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="12">
+        <v>18.396878318162912</v>
+      </c>
+      <c r="C31" s="12">
+        <v>13.252886715905554</v>
+      </c>
+      <c r="D31" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="12">
-        <v>92.566962081843926</v>
-      </c>
-      <c r="C30" s="12">
-        <v>13.252886715905554</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B31" s="12">
-        <v>18.815792505117066</v>
-      </c>
-      <c r="C31" s="12">
-        <v>22.711138133703919</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" s="13" t="s">
-        <v>65</v>
+      <c r="E31" s="19">
+        <v>2.8040034286631066</v>
+      </c>
+      <c r="F31" s="14">
+        <v>194.58</v>
+      </c>
+      <c r="G31" s="14">
+        <v>108.87</v>
+      </c>
+      <c r="H31" s="19">
+        <v>1.4575334418050874</v>
+      </c>
+      <c r="I31" s="14">
+        <v>175.87</v>
+      </c>
+      <c r="J31" s="12">
+        <v>96.13</v>
+      </c>
+      <c r="L31" s="18"/>
+      <c r="M31" s="36" t="s">
+        <v>62</v>
+      </c>
+      <c r="N31">
+        <v>2.0333486017203466</v>
+      </c>
+      <c r="O31">
+        <v>18.396878318162912</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="16" t="s">
+        <v>64</v>
       </c>
       <c r="B32" s="12">
-        <v>-30.904884695796326</v>
+        <v>99.306386647894684</v>
       </c>
       <c r="C32" s="12">
         <v>12.325664764224213</v>
       </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="13" t="s">
-        <v>67</v>
+      <c r="D32" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32" s="19">
+        <v>14.666241271003578</v>
+      </c>
+      <c r="F32" s="14">
+        <v>4243.22</v>
+      </c>
+      <c r="G32" s="14">
+        <v>1974</v>
+      </c>
+      <c r="H32" s="19">
+        <v>20.485322003885951</v>
+      </c>
+      <c r="I32" s="14">
+        <v>4276.79</v>
+      </c>
+      <c r="J32" s="13">
+        <v>1757.39</v>
+      </c>
+      <c r="L32" s="18"/>
+      <c r="M32" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="N32">
+        <v>1.3642480517204696</v>
+      </c>
+      <c r="O32">
+        <v>99.306386647894684</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="16" t="s">
+        <v>66</v>
       </c>
       <c r="B33" s="12">
-        <v>-51.876005137658588</v>
+        <v>-33.510005089560352</v>
       </c>
       <c r="C33" s="12">
         <v>6.2577972952742158</v>
       </c>
+      <c r="D33" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" s="19">
+        <v>9.212759004577574</v>
+      </c>
+      <c r="F33" s="14">
+        <v>1024.68</v>
+      </c>
+      <c r="G33" s="14">
+        <v>638.79</v>
+      </c>
+      <c r="H33" s="19">
+        <v>18.432354173037659</v>
+      </c>
+      <c r="I33" s="14">
+        <v>1016.85</v>
+      </c>
+      <c r="J33" s="12">
+        <v>601.16999999999996</v>
+      </c>
+      <c r="L33" s="18"/>
+      <c r="M33" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="N33">
+        <v>-5.5782482291754221</v>
+      </c>
+      <c r="O33">
+        <v>-33.510005089560352</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="L34" s="18"/>
+      <c r="M34" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="N34">
+        <v>-8.5366846249992854</v>
+      </c>
+      <c r="O34">
+        <v>-52.404668327341227</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="L35" s="18"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="L36" s="20"/>
+      <c r="M36" s="19"/>
+      <c r="N36" s="19"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="M3:O34">
+    <sortCondition ref="M3:M34"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4563,496 +6385,1201 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93853468-C935-EC43-93ED-52FE3BFE8F9F}">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:N37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="10"/>
-    <col min="2" max="2" width="10.83203125" style="14"/>
-    <col min="3" max="3" width="18.83203125" style="14" customWidth="1"/>
-    <col min="4" max="7" width="10.83203125" style="15"/>
-    <col min="8" max="8" width="14.1640625" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="10.83203125" style="15"/>
+    <col min="2" max="2" width="10.83203125" style="21"/>
+    <col min="3" max="3" width="18.83203125" style="21" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="23"/>
+    <col min="5" max="5" width="28.5" style="10" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="23"/>
+    <col min="7" max="7" width="19.1640625" style="23" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.1640625" style="23" customWidth="1"/>
+    <col min="9" max="9" width="26" style="23" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="10.83203125" style="24"/>
+    <col min="15" max="15" width="14.1640625" style="24" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="10.83203125" style="24"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:14">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="H1" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="J1" s="22" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="L1" s="25"/>
+      <c r="M1" s="25"/>
+      <c r="N1" s="25"/>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>102</v>
-      </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-    </row>
-    <row r="3" spans="1:7">
+        <v>106</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="G2" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="I2" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="J2" s="22" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="26"/>
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B3" s="12">
-        <v>-13.552328450957299</v>
+        <v>-10.908241681538982</v>
       </c>
       <c r="C3" s="12">
         <v>4.1152321791566804</v>
       </c>
-      <c r="E3"/>
-      <c r="F3"/>
-      <c r="G3" s="18"/>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="D3" s="22" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="19">
+        <v>58.942717461710295</v>
+      </c>
+      <c r="F3" s="22">
+        <v>7334.46</v>
+      </c>
+      <c r="G3" s="22">
+        <v>4150.75</v>
+      </c>
+      <c r="H3" s="19">
+        <v>67.589689804199438</v>
+      </c>
+      <c r="I3" s="22">
+        <v>7044.56</v>
+      </c>
+      <c r="J3" s="21">
+        <v>3540.86</v>
+      </c>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3" s="27"/>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B4" s="12">
-        <v>-48.009996979606832</v>
+        <v>-39.054435983205316</v>
       </c>
       <c r="C4" s="12">
         <v>-43.697690516644599</v>
       </c>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4" s="18"/>
-    </row>
-    <row r="5" spans="1:7">
+      <c r="D4" s="22" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="19">
+        <v>0.72296990075272094</v>
+      </c>
+      <c r="F4" s="22">
+        <v>89.47</v>
+      </c>
+      <c r="G4" s="22">
+        <v>47.78</v>
+      </c>
+      <c r="H4" s="19">
+        <v>1.322169033698475</v>
+      </c>
+      <c r="I4" s="22">
+        <v>158.91</v>
+      </c>
+      <c r="J4" s="21">
+        <v>96.13</v>
+      </c>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4" s="27"/>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B5" s="12">
-        <v>-26.996621271389444</v>
+        <v>-24.199228873172139</v>
       </c>
       <c r="C5" s="12">
         <v>-1.6276190244968201</v>
       </c>
-      <c r="E5"/>
-      <c r="F5"/>
-      <c r="G5" s="18"/>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="D5" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="19">
+        <v>10.723820296945991</v>
+      </c>
+      <c r="F5" s="22">
+        <v>2025.93</v>
+      </c>
+      <c r="G5" s="22">
+        <v>1095.9000000000001</v>
+      </c>
+      <c r="H5" s="19">
+        <v>14.166237359079625</v>
+      </c>
+      <c r="I5" s="22">
+        <v>2059.4499999999998</v>
+      </c>
+      <c r="J5" s="21">
+        <v>1055.1500000000001</v>
+      </c>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5" s="27"/>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B6" s="12">
-        <v>-51.807065661138694</v>
+        <v>-53.697913572211128</v>
       </c>
       <c r="C6" s="12">
         <v>-10.873043625690096</v>
       </c>
-      <c r="E6"/>
-      <c r="F6"/>
-      <c r="G6" s="18"/>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="D6" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" s="19">
+        <v>7.6487337451780926</v>
+      </c>
+      <c r="F6" s="22">
+        <v>841.1</v>
+      </c>
+      <c r="G6" s="22">
+        <v>510.97</v>
+      </c>
+      <c r="H6" s="19">
+        <v>15.024158698883435</v>
+      </c>
+      <c r="I6" s="22">
+        <v>943.71</v>
+      </c>
+      <c r="J6" s="21">
+        <v>534.67999999999995</v>
+      </c>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6" s="27"/>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="12">
-        <v>14.023153210134678</v>
+        <v>-32.765416216801171</v>
       </c>
       <c r="C7" s="12">
+        <v>-1.6328997758678399</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="19">
+        <v>25.221590456396985</v>
+      </c>
+      <c r="F7" s="22">
+        <v>2229.5100000000002</v>
+      </c>
+      <c r="G7" s="22">
+        <v>1285.19</v>
+      </c>
+      <c r="H7" s="19">
+        <v>36.777165732048587</v>
+      </c>
+      <c r="I7" s="22">
+        <v>2266.52</v>
+      </c>
+      <c r="J7" s="21">
+        <v>1202.48</v>
+      </c>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7" s="27"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B8" s="12">
+        <v>24.493908606401803</v>
+      </c>
+      <c r="C8" s="12">
         <v>-1.4519043066375386</v>
       </c>
-      <c r="E7"/>
-      <c r="F7"/>
-      <c r="G7" s="18"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="10" t="s">
+      <c r="D8" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="19">
+        <v>10.127456556009038</v>
+      </c>
+      <c r="F8" s="22">
+        <v>2710.93</v>
+      </c>
+      <c r="G8" s="22">
+        <v>1272.9000000000001</v>
+      </c>
+      <c r="H8" s="19">
+        <v>8.7901664995419626</v>
+      </c>
+      <c r="I8" s="22">
+        <v>2750.87</v>
+      </c>
+      <c r="J8" s="21">
+        <v>1117.47</v>
+      </c>
+      <c r="L8"/>
+      <c r="M8"/>
+      <c r="N8" s="27"/>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="B8" s="12">
-        <v>-32.692847978141245</v>
-      </c>
-      <c r="C8" s="12">
-        <v>-1.6328997758678399</v>
-      </c>
-      <c r="E8"/>
-      <c r="F8"/>
-      <c r="G8" s="18"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="10" t="s">
-        <v>76</v>
-      </c>
       <c r="B9" s="12">
-        <v>-33.754661353328643</v>
+        <v>-33.508814584473754</v>
       </c>
       <c r="C9" s="12">
         <v>-4.6874211954420399</v>
       </c>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9" s="18"/>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="D9" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="19">
+        <v>25.123575264253095</v>
+      </c>
+      <c r="F9" s="22">
+        <v>2834.72</v>
+      </c>
+      <c r="G9" s="22">
+        <v>1395.36</v>
+      </c>
+      <c r="H9" s="19">
+        <v>36.465396659791907</v>
+      </c>
+      <c r="I9" s="22">
+        <v>2974.13</v>
+      </c>
+      <c r="J9" s="21">
+        <v>1450.71</v>
+      </c>
+      <c r="L9"/>
+      <c r="M9"/>
+      <c r="N9" s="27"/>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B10" s="12">
-        <v>-24.338366669958759</v>
+        <v>-22.059299812443346</v>
       </c>
       <c r="C10" s="12">
         <v>-10.257986450373032</v>
       </c>
-      <c r="E10"/>
-      <c r="F10"/>
-      <c r="G10" s="18"/>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="D10" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="19">
+        <v>10.211564386096354</v>
+      </c>
+      <c r="F10" s="22">
+        <v>2773.8</v>
+      </c>
+      <c r="G10" s="22">
+        <v>1119.68</v>
+      </c>
+      <c r="H10" s="19">
+        <v>12.941308712276129</v>
+      </c>
+      <c r="I10" s="22">
+        <v>3090.86</v>
+      </c>
+      <c r="J10" s="21">
+        <v>1075.75</v>
+      </c>
+      <c r="L10"/>
+      <c r="M10"/>
+      <c r="N10" s="27"/>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B11" s="12">
-        <v>-42.814133603304789</v>
+        <v>-45.013229554106914</v>
       </c>
       <c r="C11" s="12">
         <v>-25.140230388267177</v>
       </c>
-      <c r="E11"/>
-      <c r="F11"/>
-      <c r="G11" s="18"/>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="D11" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="19">
+        <v>3.6373529412489014</v>
+      </c>
+      <c r="F11" s="22">
+        <v>273.58999999999997</v>
+      </c>
+      <c r="G11" s="22">
+        <v>147.02000000000001</v>
+      </c>
+      <c r="H11" s="19">
+        <v>6.1539249676148096</v>
+      </c>
+      <c r="I11" s="22">
+        <v>365.47</v>
+      </c>
+      <c r="J11" s="21">
+        <v>168.55</v>
+      </c>
+      <c r="L11"/>
+      <c r="M11"/>
+      <c r="N11" s="27"/>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B12" s="12">
-        <v>-15.479326106626401</v>
+        <v>-9.866823968841091</v>
       </c>
       <c r="C12" s="12">
         <v>-2.3024463776538764</v>
       </c>
-      <c r="E12"/>
-      <c r="F12"/>
-      <c r="G12" s="18"/>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="D12" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="19">
+        <v>39.568015713843018</v>
+      </c>
+      <c r="F12" s="22">
+        <v>6455.19</v>
+      </c>
+      <c r="G12" s="22">
+        <v>3809.92</v>
+      </c>
+      <c r="H12" s="19">
+        <v>45.027186769139277</v>
+      </c>
+      <c r="I12" s="22">
+        <v>6607.32</v>
+      </c>
+      <c r="J12" s="28">
+        <v>3584.87</v>
+      </c>
+      <c r="L12"/>
+      <c r="M12"/>
+      <c r="N12" s="27"/>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="10" t="s">
         <v>80</v>
       </c>
       <c r="B13" s="12">
-        <v>7.482185906298783</v>
+        <v>-10.273768520162353</v>
       </c>
       <c r="C13" s="12">
+        <v>0.82131876534831805</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="19">
+        <v>70.717559493479058</v>
+      </c>
+      <c r="F13" s="22">
+        <v>10785.29</v>
+      </c>
+      <c r="G13" s="22">
+        <v>6624.27</v>
+      </c>
+      <c r="H13" s="19">
+        <v>80.226043691123976</v>
+      </c>
+      <c r="I13" s="23">
+        <v>10697.43</v>
+      </c>
+      <c r="J13" s="21">
+        <v>6023.8</v>
+      </c>
+      <c r="L13"/>
+      <c r="M13"/>
+      <c r="N13" s="27"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="A14" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B14" s="12">
+        <v>7.0020943283850281</v>
+      </c>
+      <c r="C14" s="12">
         <v>8.6002345391276727</v>
       </c>
-      <c r="E13"/>
-      <c r="F13"/>
-      <c r="G13" s="18"/>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="10" t="s">
+      <c r="D14" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="19">
+        <v>94.394767008528305</v>
+      </c>
+      <c r="F14" s="22">
+        <v>14743.09</v>
+      </c>
+      <c r="G14" s="22">
+        <v>7788.22</v>
+      </c>
+      <c r="H14" s="19">
+        <v>88.598402348027378</v>
+      </c>
+      <c r="I14" s="22">
+        <v>13575.56</v>
+      </c>
+      <c r="J14" s="21">
+        <v>7055.11</v>
+      </c>
+      <c r="L14"/>
+      <c r="M14"/>
+      <c r="N14" s="27"/>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="A15" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B14" s="12">
-        <v>-14.862464573612574</v>
-      </c>
-      <c r="C14" s="12">
-        <v>0.82131876534831805</v>
-      </c>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="G14" s="18"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="10" t="s">
-        <v>82</v>
-      </c>
       <c r="B15" s="12">
-        <v>-17.180589001146796</v>
+        <v>-13.269693508731194</v>
       </c>
       <c r="C15" s="12">
         <v>6.5745143322918045</v>
       </c>
-      <c r="E15"/>
-      <c r="F15"/>
-      <c r="G15" s="18"/>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="D15" s="22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="19">
+        <v>46.163253907706853</v>
+      </c>
+      <c r="F15" s="22">
+        <v>4706.97</v>
+      </c>
+      <c r="G15" s="22">
+        <v>2777.04</v>
+      </c>
+      <c r="H15" s="19">
+        <v>54.841944976184379</v>
+      </c>
+      <c r="I15" s="22">
+        <v>4416.6000000000004</v>
+      </c>
+      <c r="J15" s="21">
+        <v>2586.21</v>
+      </c>
+      <c r="L15"/>
+      <c r="M15"/>
+      <c r="N15" s="27"/>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B16" s="12">
-        <v>-40.42416183496568</v>
+        <v>-39.969343126548587</v>
       </c>
       <c r="C16" s="12">
         <v>-4.9203691025331429</v>
       </c>
-      <c r="E16"/>
-      <c r="F16"/>
-      <c r="G16" s="18"/>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="D16" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="19">
+        <v>44.958510439192324</v>
+      </c>
+      <c r="F16" s="22">
+        <v>4763.4799999999996</v>
+      </c>
+      <c r="G16" s="22">
+        <v>3068.01</v>
+      </c>
+      <c r="H16" s="19">
+        <v>73.419802218351592</v>
+      </c>
+      <c r="I16" s="22">
+        <v>5009.99</v>
+      </c>
+      <c r="J16" s="21">
+        <v>2989.54</v>
+      </c>
+      <c r="L16"/>
+      <c r="M16"/>
+      <c r="N16" s="27"/>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="12">
+        <v>8.6564142307003227</v>
+      </c>
+      <c r="C17" s="12">
+        <v>13.514287662824787</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="19">
+        <v>34.218511569548681</v>
+      </c>
+      <c r="F17" s="22">
+        <v>5825.61</v>
+      </c>
+      <c r="G17" s="22">
+        <v>4186.5</v>
+      </c>
+      <c r="H17" s="19">
+        <v>32.051579718799999</v>
+      </c>
+      <c r="I17" s="22">
+        <v>5132.05</v>
+      </c>
+      <c r="J17" s="21">
+        <v>3763.3</v>
+      </c>
+      <c r="L17"/>
+      <c r="M17"/>
+      <c r="N17" s="27"/>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B17" s="12">
-        <v>3.8169340713046673</v>
-      </c>
-      <c r="C17" s="12">
-        <v>11.700455294902191</v>
-      </c>
-      <c r="E17"/>
-      <c r="F17"/>
-      <c r="G17" s="18"/>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="10" t="s">
-        <v>85</v>
-      </c>
       <c r="B18" s="12">
-        <v>-21.886507966311594</v>
+        <v>-19.987346437828911</v>
       </c>
       <c r="C18" s="12">
         <v>-0.29733965027890485</v>
       </c>
-      <c r="E18"/>
-      <c r="F18"/>
-      <c r="G18" s="18"/>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="D18" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="19">
+        <v>50.054313882637047</v>
+      </c>
+      <c r="F18" s="22">
+        <v>5458.94</v>
+      </c>
+      <c r="G18" s="22">
+        <v>3797.7</v>
+      </c>
+      <c r="H18" s="19">
+        <v>63.465668463645422</v>
+      </c>
+      <c r="I18" s="22">
+        <v>5475.22</v>
+      </c>
+      <c r="J18" s="28">
+        <v>3440.82</v>
+      </c>
+      <c r="L18"/>
+      <c r="M18"/>
+      <c r="N18" s="27"/>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B19" s="12">
-        <v>-34.17183554247616</v>
+        <v>-33.754386138783346</v>
       </c>
       <c r="C19" s="12">
         <v>-2.5693594613357879E-2</v>
       </c>
-      <c r="E19"/>
-      <c r="F19"/>
-      <c r="G19" s="18"/>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="D19" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="19">
+        <v>37.911175699307741</v>
+      </c>
+      <c r="F19" s="22">
+        <v>3774.29</v>
+      </c>
+      <c r="G19" s="22">
+        <v>2198.31</v>
+      </c>
+      <c r="H19" s="19">
+        <v>57.030148987724132</v>
+      </c>
+      <c r="I19" s="22">
+        <v>3775.26</v>
+      </c>
+      <c r="J19" s="21">
+        <v>2182.37</v>
+      </c>
+      <c r="L19"/>
+      <c r="M19"/>
+      <c r="N19" s="27"/>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" s="10" t="s">
         <v>87</v>
       </c>
       <c r="B20" s="12">
-        <v>6.5085396367223698</v>
+        <v>-11.160110248842416</v>
       </c>
       <c r="C20" s="12">
-        <v>13.514287662824787</v>
-      </c>
-      <c r="E20"/>
-      <c r="F20"/>
-      <c r="G20" s="18"/>
-    </row>
-    <row r="21" spans="1:7">
+        <v>4.8637037644838506</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="19">
+        <v>20.796616893488086</v>
+      </c>
+      <c r="F20" s="22">
+        <v>3578.39</v>
+      </c>
+      <c r="G20" s="22">
+        <v>2563.4</v>
+      </c>
+      <c r="H20" s="19">
+        <v>23.792580607606514</v>
+      </c>
+      <c r="I20" s="22">
+        <v>3412.42</v>
+      </c>
+      <c r="J20" s="21">
+        <v>2353.31</v>
+      </c>
+      <c r="L20"/>
+      <c r="M20"/>
+      <c r="N20" s="27"/>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="12">
+        <v>5.0508988393068286</v>
+      </c>
+      <c r="C21" s="12">
+        <v>11.700455294902191</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E21" s="19">
+        <v>23.558404117466363</v>
+      </c>
+      <c r="F21" s="22">
+        <v>6984.73</v>
+      </c>
+      <c r="G21" s="22">
+        <v>3957.84</v>
+      </c>
+      <c r="H21" s="19">
+        <v>22.700133116628844</v>
+      </c>
+      <c r="I21" s="22">
+        <v>6253.09</v>
+      </c>
+      <c r="J21" s="21">
+        <v>3070.48</v>
+      </c>
+      <c r="L21"/>
+      <c r="M21"/>
+      <c r="N21" s="27"/>
+    </row>
+    <row r="22" spans="1:14">
+      <c r="A22" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B21" s="12">
-        <v>-16.130478622372099</v>
-      </c>
-      <c r="C21" s="12">
-        <v>4.8637037644838506</v>
-      </c>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21" s="18"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="10" t="s">
-        <v>89</v>
-      </c>
       <c r="B22" s="12">
-        <v>-11.311345094000066</v>
+        <v>-6.4731578826205478</v>
       </c>
       <c r="C22" s="12">
         <v>-8.1901057171965732</v>
       </c>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22" s="18"/>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="D22" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="19">
+        <v>3.7048392097787901</v>
+      </c>
+      <c r="F22" s="22">
+        <v>693.89</v>
+      </c>
+      <c r="G22" s="22">
+        <v>378.8</v>
+      </c>
+      <c r="H22" s="19">
+        <v>4.0777579463742786</v>
+      </c>
+      <c r="I22" s="22">
+        <v>755.79</v>
+      </c>
+      <c r="J22" s="28">
+        <v>373.29</v>
+      </c>
+      <c r="L22"/>
+      <c r="M22"/>
+      <c r="N22" s="27"/>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B23" s="12">
-        <v>-4.4585510012684244</v>
+        <v>-1.1867511328897018</v>
       </c>
       <c r="C23" s="12">
         <v>7.8604782793264372</v>
       </c>
-      <c r="E23"/>
-      <c r="F23"/>
-      <c r="G23" s="18"/>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="D23" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="19">
+        <v>1.5875475900252078</v>
+      </c>
+      <c r="F23" s="22">
+        <v>304.89999999999998</v>
+      </c>
+      <c r="G23" s="22">
+        <v>116.23</v>
+      </c>
+      <c r="H23" s="19">
+        <v>1.643633479723327</v>
+      </c>
+      <c r="I23" s="22">
+        <v>282.68</v>
+      </c>
+      <c r="J23" s="21">
+        <v>103.55</v>
+      </c>
+      <c r="L23"/>
+      <c r="M23"/>
+      <c r="N23" s="27"/>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="12">
+        <v>-21.418962654272537</v>
+      </c>
+      <c r="C24" s="12">
+        <v>2.137822910303623</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>57</v>
+      </c>
+      <c r="E24" s="19">
+        <v>33.370951281191928</v>
+      </c>
+      <c r="F24" s="22">
+        <v>6403.97</v>
+      </c>
+      <c r="G24" s="22">
+        <v>3593.76</v>
+      </c>
+      <c r="H24" s="19">
+        <v>42.593194703396861</v>
+      </c>
+      <c r="I24" s="22">
+        <v>6269.93</v>
+      </c>
+      <c r="J24" s="21">
+        <v>3336.06</v>
+      </c>
+      <c r="L24"/>
+      <c r="M24"/>
+      <c r="N24" s="27"/>
+    </row>
+    <row r="25" spans="1:14">
+      <c r="A25" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B24" s="12">
-        <v>-7.9165947335311975</v>
-      </c>
-      <c r="C24" s="12">
-        <v>-2.0453065205486665</v>
-      </c>
-      <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24" s="18"/>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="10" t="s">
-        <v>92</v>
-      </c>
       <c r="B25" s="12">
-        <v>-12.794744325511898</v>
+        <v>-5.9193554767627585</v>
       </c>
       <c r="C25" s="12">
         <v>4.7494998488931701</v>
       </c>
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25" s="18"/>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="D25" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="19">
+        <v>49.924356130133489</v>
+      </c>
+      <c r="F25" s="22">
+        <v>8387.9</v>
+      </c>
+      <c r="G25" s="22">
+        <v>5655.28</v>
+      </c>
+      <c r="H25" s="19">
+        <v>54.996708211331125</v>
+      </c>
+      <c r="I25" s="23">
+        <v>8007.58</v>
+      </c>
+      <c r="J25" s="21">
+        <v>4883.4399999999996</v>
+      </c>
+      <c r="L25"/>
+      <c r="M25"/>
+      <c r="N25" s="27"/>
+    </row>
+    <row r="26" spans="1:14">
       <c r="A26" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B26" s="12">
-        <v>-32.485945675399265</v>
+        <v>-30.539612080888904</v>
       </c>
       <c r="C26" s="12">
         <v>-33.244094488188978</v>
       </c>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26" s="18"/>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="D26" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="E26" s="19">
+        <v>1.6271182138652531</v>
+      </c>
+      <c r="F26" s="22">
+        <v>127.17</v>
+      </c>
+      <c r="G26" s="22">
+        <v>101.86</v>
+      </c>
+      <c r="H26" s="19">
+        <v>2.3934615189759056</v>
+      </c>
+      <c r="I26" s="22">
+        <v>190.5</v>
+      </c>
+      <c r="J26" s="21">
+        <v>128.65</v>
+      </c>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="N26" s="27"/>
+    </row>
+    <row r="27" spans="1:14">
       <c r="A27" s="10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="B27" s="12">
-        <v>-10.076569629941964</v>
+        <v>-5.2464035044651594</v>
       </c>
       <c r="C27" s="12">
+        <v>-2.0453065205486665</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="E27" s="19">
+        <v>12.367138769613588</v>
+      </c>
+      <c r="F27" s="22">
+        <v>3022.97</v>
+      </c>
+      <c r="G27" s="22">
+        <v>1323.66</v>
+      </c>
+      <c r="H27" s="19">
+        <v>13.098073555534492</v>
+      </c>
+      <c r="I27" s="22">
+        <v>3086.09</v>
+      </c>
+      <c r="J27" s="21">
+        <v>1210.55</v>
+      </c>
+      <c r="L27"/>
+      <c r="M27"/>
+      <c r="N27" s="27"/>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" s="12">
+        <v>-0.67770060168819746</v>
+      </c>
+      <c r="C28" s="12">
         <v>-2.5958338469123565</v>
       </c>
-      <c r="E27"/>
-      <c r="F27"/>
-      <c r="G27" s="18"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="10" t="s">
+      <c r="D28" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="19">
+        <v>8.5284683512363202</v>
+      </c>
+      <c r="F28" s="22">
+        <v>3160.96</v>
+      </c>
+      <c r="G28" s="22">
+        <v>1478.09</v>
+      </c>
+      <c r="H28" s="19">
+        <v>9.11514717438234</v>
+      </c>
+      <c r="I28" s="22">
+        <v>3245.2</v>
+      </c>
+      <c r="J28" s="21">
+        <v>1362.01</v>
+      </c>
+      <c r="L28"/>
+      <c r="M28"/>
+      <c r="N28" s="27"/>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="B28" s="12">
-        <v>-24.323943231925437</v>
-      </c>
-      <c r="C28" s="12">
-        <v>2.137822910303623</v>
-      </c>
-      <c r="E28"/>
-      <c r="F28"/>
-      <c r="G28" s="18"/>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="10" t="s">
-        <v>96</v>
-      </c>
       <c r="B29" s="12">
-        <v>-46.942206963042295</v>
+        <v>-29.310824267814095</v>
       </c>
       <c r="C29" s="12">
         <v>16.785938856783524</v>
       </c>
-      <c r="E29"/>
-      <c r="F29"/>
-      <c r="G29" s="18"/>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="D29" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="E29" s="19">
+        <v>1.3807077502937468</v>
+      </c>
+      <c r="F29" s="22">
+        <v>390.03</v>
+      </c>
+      <c r="G29" s="22">
+        <v>255.73</v>
+      </c>
+      <c r="H29" s="19">
+        <v>2.1158812976732269</v>
+      </c>
+      <c r="I29" s="22">
+        <v>333.97</v>
+      </c>
+      <c r="J29" s="21">
+        <v>177.44</v>
+      </c>
+      <c r="L29"/>
+      <c r="M29"/>
+      <c r="N29" s="27"/>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="B30" s="12">
+        <v>16.173490579800699</v>
+      </c>
+      <c r="C30" s="12">
+        <v>25.1616162063725</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="E30" s="19">
+        <v>16.357622467507575</v>
+      </c>
+      <c r="F30" s="22">
+        <v>2824.76</v>
+      </c>
+      <c r="G30" s="22">
+        <v>2119.16</v>
+      </c>
+      <c r="H30" s="19">
+        <v>13.736661279180067</v>
+      </c>
+      <c r="I30" s="22">
+        <v>2256.89</v>
+      </c>
+      <c r="J30" s="28">
+        <v>1726.95</v>
+      </c>
+      <c r="L30"/>
+      <c r="M30"/>
+      <c r="N30" s="27"/>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="12">
+        <v>18.396878318162912</v>
+      </c>
+      <c r="C31" s="12">
+        <v>10.638539830556665</v>
+      </c>
+      <c r="D31" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="B30" s="12">
-        <v>92.566962081843926</v>
-      </c>
-      <c r="C30" s="12">
-        <v>10.638539830556665</v>
-      </c>
-      <c r="E30"/>
-      <c r="F30"/>
-      <c r="G30" s="18"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="B31" s="12">
-        <v>18.815792505117066</v>
-      </c>
-      <c r="C31" s="12">
-        <v>25.1616162063725</v>
-      </c>
-      <c r="E31"/>
-      <c r="F31"/>
-      <c r="G31" s="18"/>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="E31" s="19">
+        <v>2.8040034286631066</v>
+      </c>
+      <c r="F31" s="22">
+        <v>194.58</v>
+      </c>
+      <c r="G31" s="22">
+        <v>108.87</v>
+      </c>
+      <c r="H31" s="19">
+        <v>1.4575334418050874</v>
+      </c>
+      <c r="I31" s="22">
+        <v>175.87</v>
+      </c>
+      <c r="J31" s="21">
+        <v>96.13</v>
+      </c>
+      <c r="L31"/>
+      <c r="M31"/>
+      <c r="N31" s="27"/>
+    </row>
+    <row r="32" spans="1:14">
       <c r="A32" s="10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B32" s="12">
-        <v>-30.904884695796326</v>
+        <v>99.306386647894684</v>
       </c>
       <c r="C32" s="12">
         <v>-0.78493449526396453</v>
       </c>
-      <c r="E32"/>
-      <c r="F32"/>
-      <c r="G32" s="18"/>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="D32" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32" s="19">
+        <v>14.666241271003578</v>
+      </c>
+      <c r="F32" s="22">
+        <v>4243.22</v>
+      </c>
+      <c r="G32" s="22">
+        <v>1974</v>
+      </c>
+      <c r="H32" s="19">
+        <v>20.485322003885951</v>
+      </c>
+      <c r="I32" s="22">
+        <v>4276.79</v>
+      </c>
+      <c r="J32" s="28">
+        <v>1757.39</v>
+      </c>
+      <c r="L32"/>
+      <c r="M32"/>
+      <c r="N32" s="27"/>
+    </row>
+    <row r="33" spans="1:14">
       <c r="A33" s="10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B33" s="12">
-        <v>-51.876005137658588</v>
+        <v>-33.510005089560352</v>
       </c>
       <c r="C33" s="12">
         <v>0.77002507744505488</v>
       </c>
-      <c r="E33"/>
-      <c r="F33"/>
-      <c r="G33" s="18"/>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="E34" s="17"/>
-      <c r="F34" s="18"/>
-      <c r="G34" s="18"/>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="E35" s="17"/>
-      <c r="F35" s="18"/>
-      <c r="G35" s="18"/>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="D33" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" s="19">
+        <v>9.212759004577574</v>
+      </c>
+      <c r="F33" s="22">
+        <v>1024.68</v>
+      </c>
+      <c r="G33" s="22">
+        <v>638.79</v>
+      </c>
+      <c r="H33" s="19">
+        <v>18.432354173037659</v>
+      </c>
+      <c r="I33" s="22">
+        <v>1016.85</v>
+      </c>
+      <c r="J33" s="21">
+        <v>601.16999999999996</v>
+      </c>
+      <c r="L33"/>
+      <c r="M33"/>
+      <c r="N33" s="27"/>
+    </row>
+    <row r="34" spans="1:14">
+      <c r="L34" s="26"/>
+      <c r="M34" s="27"/>
+      <c r="N34" s="27"/>
+    </row>
+    <row r="35" spans="1:14">
+      <c r="L35" s="26"/>
+      <c r="M35" s="27"/>
+      <c r="N35" s="27"/>
+    </row>
+    <row r="36" spans="1:14">
       <c r="B36" s="12"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="18"/>
-      <c r="G36" s="18"/>
+      <c r="L36" s="29"/>
+      <c r="M36" s="27"/>
+      <c r="N36" s="27"/>
+    </row>
+    <row r="37" spans="1:14">
+      <c r="G37" s="15"/>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:N33">
+    <sortCondition ref="A3:A33"/>
+  </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
